--- a/database/event/2567/event_2567_evp_summary.xlsx
+++ b/database/event/2567/event_2567_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>0.901</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5538</v>
+        <v>1.504</v>
       </c>
       <c r="E2" t="n">
         <v>4.8894</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.6162</v>
+        <v>4.7545</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8506</v>
+        <v>0.8761</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4435</v>
+        <v>1.4503</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6162</v>
+        <v>4.7545</v>
       </c>
       <c r="F3" t="n">
-        <v>1.323</v>
+        <v>1.4613</v>
       </c>
       <c r="G3" t="n">
         <v>3.2932</v>
       </c>
       <c r="H3" t="n">
-        <v>1.323</v>
+        <v>1.4613</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0724</v>
+        <v>1.1844</v>
       </c>
       <c r="J3" t="n">
         <v>3.2932</v>
@@ -575,7 +575,7 @@
         <v>161</v>
       </c>
       <c r="M3" t="n">
-        <v>4.365600000000001</v>
+        <v>4.4776</v>
       </c>
       <c r="N3" t="n">
         <v>232</v>
@@ -594,7 +594,7 @@
         <v>0.7501</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2232</v>
+        <v>1.1779</v>
       </c>
       <c r="E4" t="n">
         <v>4.0708</v>
@@ -640,7 +640,7 @@
         <v>0.7194</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1557</v>
+        <v>1.1114</v>
       </c>
       <c r="E5" t="n">
         <v>3.9038</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8703</v>
+        <v>3.8848</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7131999999999999</v>
+        <v>0.7159</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1422</v>
+        <v>1.1038</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8703</v>
+        <v>3.8848</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5534</v>
+        <v>3.455</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3169</v>
+        <v>0.4298</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5534</v>
+        <v>3.455</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2591</v>
+        <v>2.8004</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3169</v>
+        <v>0.4298</v>
       </c>
       <c r="K6" t="n">
         <v>71</v>
@@ -713,7 +713,7 @@
         <v>161</v>
       </c>
       <c r="M6" t="n">
-        <v>3.576</v>
+        <v>3.2302</v>
       </c>
       <c r="N6" t="n">
         <v>232</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2228</v>
+        <v>3.8724</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5939</v>
+        <v>0.7136</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8806</v>
+        <v>1.0989</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2228</v>
+        <v>3.8724</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4281</v>
+        <v>1.5555</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7947</v>
+        <v>2.3169</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4281</v>
+        <v>1.5555</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1575</v>
+        <v>1.2608</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7947</v>
+        <v>2.3169</v>
       </c>
       <c r="K7" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="L7" t="n">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9522</v>
+        <v>3.5777</v>
       </c>
       <c r="N7" t="n">
-        <v>187</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1863</v>
+        <v>3.3933</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5871</v>
+        <v>0.6253</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8658</v>
+        <v>0.908</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1863</v>
+        <v>3.3933</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7565</v>
+        <v>1.5986</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4298</v>
+        <v>1.7947</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7565</v>
+        <v>1.5986</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2342</v>
+        <v>1.2957</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4298</v>
+        <v>1.7947</v>
       </c>
       <c r="K8" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="L8" t="n">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="M8" t="n">
-        <v>2.664</v>
+        <v>3.0904</v>
       </c>
       <c r="N8" t="n">
-        <v>232</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9">
@@ -824,7 +824,7 @@
         <v>0.5524</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7897</v>
+        <v>0.7504999999999999</v>
       </c>
       <c r="E9" t="n">
         <v>2.9979</v>
@@ -870,7 +870,7 @@
         <v>0.5407999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7643</v>
+        <v>0.7254</v>
       </c>
       <c r="E10" t="n">
         <v>2.9349</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3887</v>
+        <v>2.6071</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4402</v>
+        <v>0.4804</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5436</v>
+        <v>0.5948</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3887</v>
+        <v>2.6071</v>
       </c>
       <c r="F11" t="n">
-        <v>1.449</v>
+        <v>1.6674</v>
       </c>
       <c r="G11" t="n">
         <v>0.9397</v>
       </c>
       <c r="H11" t="n">
-        <v>1.449</v>
+        <v>1.6674</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1745</v>
+        <v>1.3515</v>
       </c>
       <c r="J11" t="n">
         <v>0.9397</v>
@@ -943,7 +943,7 @@
         <v>137</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1142</v>
+        <v>2.2912</v>
       </c>
       <c r="N11" t="n">
         <v>187</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.207</v>
+        <v>2.2466</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4067</v>
+        <v>0.414</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4702</v>
+        <v>0.4511</v>
       </c>
       <c r="E12" t="n">
-        <v>2.207</v>
+        <v>2.2466</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3949</v>
+        <v>1.4345</v>
       </c>
       <c r="G12" t="n">
         <v>0.8121</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3949</v>
+        <v>1.4345</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1306</v>
+        <v>1.1627</v>
       </c>
       <c r="J12" t="n">
         <v>0.8121</v>
@@ -989,7 +989,7 @@
         <v>137</v>
       </c>
       <c r="M12" t="n">
-        <v>1.9427</v>
+        <v>1.9748</v>
       </c>
       <c r="N12" t="n">
         <v>187</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1471</v>
+        <v>2.1924</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3956</v>
+        <v>0.404</v>
       </c>
       <c r="D13" t="n">
-        <v>0.446</v>
+        <v>0.4295</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1471</v>
+        <v>2.1924</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7147</v>
+        <v>1.76</v>
       </c>
       <c r="G13" t="n">
         <v>0.4324</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7147</v>
+        <v>1.76</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3898</v>
+        <v>1.4265</v>
       </c>
       <c r="J13" t="n">
         <v>0.4324</v>
@@ -1035,7 +1035,7 @@
         <v>161</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8222</v>
+        <v>1.8589</v>
       </c>
       <c r="N13" t="n">
         <v>232</v>
@@ -1054,7 +1054,7 @@
         <v>0.387</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4271</v>
+        <v>0.3928</v>
       </c>
       <c r="E14" t="n">
         <v>2.1003</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6796</v>
+        <v>2.0193</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3095</v>
+        <v>0.3721</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2572</v>
+        <v>0.3606</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6796</v>
+        <v>2.0193</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6796</v>
+        <v>2.0193</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6796</v>
+        <v>2.0193</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6796</v>
+        <v>2.0193</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6796</v>
+        <v>2.0193</v>
       </c>
       <c r="N15" t="n">
         <v>131</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5829</v>
+        <v>1.833</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2917</v>
+        <v>0.3378</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2181</v>
+        <v>0.2864</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5829</v>
+        <v>1.833</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3849</v>
+        <v>1.635</v>
       </c>
       <c r="G16" t="n">
         <v>0.198</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3849</v>
+        <v>1.635</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1225</v>
+        <v>1.3252</v>
       </c>
       <c r="J16" t="n">
         <v>0.198</v>
@@ -1173,7 +1173,7 @@
         <v>137</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3205</v>
+        <v>1.5232</v>
       </c>
       <c r="N16" t="n">
         <v>187</v>
@@ -1182,323 +1182,323 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2117</v>
+        <v>1.4298</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2233</v>
+        <v>0.2635</v>
       </c>
       <c r="D17" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.1257</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2117</v>
+        <v>1.4298</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9393</v>
+        <v>1.4298</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2724</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9393</v>
+        <v>1.4298</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7613</v>
+        <v>1.4298</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2724</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>183</v>
+        <v>92</v>
       </c>
       <c r="L17" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0337</v>
+        <v>1.4298</v>
       </c>
       <c r="N17" t="n">
-        <v>288</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0411</v>
+        <v>1.2117</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1918</v>
+        <v>0.2233</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0008</v>
+        <v>0.0388</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0411</v>
+        <v>1.2117</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0411</v>
+        <v>0.9393</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.2724</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0411</v>
+        <v>0.9393</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0411</v>
+        <v>0.7613</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.2724</v>
       </c>
       <c r="K18" t="n">
-        <v>102</v>
+        <v>183</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0411</v>
+        <v>1.0337</v>
       </c>
       <c r="N18" t="n">
-        <v>102</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0167</v>
+        <v>1.0411</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1873</v>
+        <v>0.1918</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0106</v>
+        <v>-0.0291</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0167</v>
+        <v>1.0411</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9125</v>
+        <v>1.0411</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8958</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9125</v>
+        <v>1.0411</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5501</v>
+        <v>1.0411</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8958</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="L19" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6543</v>
+        <v>1.0411</v>
       </c>
       <c r="N19" t="n">
-        <v>221</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9504</v>
+        <v>1.0167</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1751</v>
+        <v>0.1873</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0374</v>
+        <v>-0.0389</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9504</v>
+        <v>1.0167</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9504</v>
+        <v>1.9125</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.8958</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9504</v>
+        <v>1.9125</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9504</v>
+        <v>1.5501</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.8958</v>
       </c>
       <c r="K20" t="n">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9504</v>
+        <v>0.6543</v>
       </c>
       <c r="N20" t="n">
-        <v>102</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8257</v>
+        <v>0.9524</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1522</v>
+        <v>0.1755</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0878</v>
+        <v>-0.0645</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8257</v>
+        <v>0.9524</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0032</v>
+        <v>0.9524</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8225</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0032</v>
+        <v>0.9524</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0026</v>
+        <v>0.9524</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8225</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="L21" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8251000000000001</v>
+        <v>0.9524</v>
       </c>
       <c r="N21" t="n">
-        <v>187</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5716</v>
+        <v>0.8257</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1053</v>
+        <v>0.1522</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1904</v>
+        <v>-0.115</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5716</v>
+        <v>0.8257</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5716</v>
+        <v>0.0032</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.8225</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5716</v>
+        <v>0.0032</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5716</v>
+        <v>0.0026</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.8225</v>
       </c>
       <c r="K22" t="n">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5716</v>
+        <v>0.8251000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>92</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.5981</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0935</v>
+        <v>0.1102</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2163</v>
+        <v>-0.2056</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.5981</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.5981</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.5981</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.5981</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.5981</v>
       </c>
       <c r="N23" t="n">
-        <v>131</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4357</v>
+        <v>0.5831</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0803</v>
+        <v>0.1074</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2453</v>
+        <v>-0.2116</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4357</v>
+        <v>0.5831</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4357</v>
+        <v>0.5831</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4357</v>
+        <v>0.5831</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4357</v>
+        <v>0.5831</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4357</v>
+        <v>0.5831</v>
       </c>
       <c r="N24" t="n">
         <v>131</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1462</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0269</v>
+        <v>0.0935</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3623</v>
+        <v>-0.2417</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1462</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1462</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1462</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1462</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1462</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>102</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.2818</v>
+        <v>0.1462</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0519</v>
+        <v>0.0269</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5352</v>
+        <v>-0.3857</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2818</v>
+        <v>0.1462</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2818</v>
+        <v>0.1462</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2818</v>
+        <v>0.1462</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2818</v>
+        <v>0.1462</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2818</v>
+        <v>0.1462</v>
       </c>
       <c r="N26" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27">
@@ -1652,7 +1652,7 @@
         <v>-0.0589</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5506</v>
+        <v>-0.5714</v>
       </c>
       <c r="E27" t="n">
         <v>-0.3199</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0614</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.556</v>
+        <v>-0.5767</v>
       </c>
       <c r="E28" t="n">
         <v>-0.3332</v>
@@ -1734,185 +1734,185 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4293</v>
+        <v>-0.3693</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0791</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5948</v>
+        <v>-0.591</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4293</v>
+        <v>-0.3693</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.4293</v>
+        <v>-0.3693</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4293</v>
+        <v>-0.3693</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4293</v>
+        <v>-0.3693</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4293</v>
+        <v>-0.3693</v>
       </c>
       <c r="N29" t="n">
-        <v>102</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4625</v>
+        <v>-0.4293</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0852</v>
+        <v>-0.0791</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6082</v>
+        <v>-0.6149</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4625</v>
+        <v>-0.4293</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4625</v>
+        <v>-0.4293</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4625</v>
+        <v>-0.4293</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4625</v>
+        <v>-0.4293</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4625</v>
+        <v>-0.4293</v>
       </c>
       <c r="N30" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.579</v>
+        <v>-0.4625</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1067</v>
+        <v>-0.0852</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6553</v>
+        <v>-0.6282</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.579</v>
+        <v>-0.4625</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.579</v>
+        <v>-0.4625</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.579</v>
+        <v>-0.4625</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.579</v>
+        <v>-0.4625</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.579</v>
+        <v>-0.4625</v>
       </c>
       <c r="N31" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6583</v>
+        <v>-0.579</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1213</v>
+        <v>-0.1067</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6873</v>
+        <v>-0.6746</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6583</v>
+        <v>-0.579</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6583</v>
+        <v>-0.579</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6583</v>
+        <v>-0.579</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6583</v>
+        <v>-0.579</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6583</v>
+        <v>-0.579</v>
       </c>
       <c r="N32" t="n">
-        <v>131</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33">
@@ -1928,7 +1928,7 @@
         <v>-0.1266</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.699</v>
+        <v>-0.7177</v>
       </c>
       <c r="E33" t="n">
         <v>-0.6873</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1402</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7288</v>
+        <v>-0.7471</v>
       </c>
       <c r="E34" t="n">
         <v>-0.761</v>
@@ -2020,7 +2020,7 @@
         <v>-0.1539</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7588</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="E35" t="n">
         <v>-0.8353</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8865</v>
+        <v>-0.8517</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1634</v>
+        <v>-0.1569</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7795</v>
+        <v>-0.7832</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8865</v>
+        <v>-0.8517</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8865</v>
+        <v>-0.8517</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8865</v>
+        <v>-0.8517</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8865</v>
+        <v>-0.8517</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8865</v>
+        <v>-0.8517</v>
       </c>
       <c r="N36" t="n">
         <v>92</v>
@@ -2112,7 +2112,7 @@
         <v>-0.2056</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8721</v>
+        <v>-0.8884</v>
       </c>
       <c r="E37" t="n">
         <v>-1.1157</v>
@@ -2158,7 +2158,7 @@
         <v>-0.2229</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9101</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="E38" t="n">
         <v>-1.2097</v>
@@ -2204,7 +2204,7 @@
         <v>-0.2562</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.983</v>
+        <v>-0.9978</v>
       </c>
       <c r="E39" t="n">
         <v>-1.3903</v>
@@ -2250,7 +2250,7 @@
         <v>-0.2892</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0554</v>
+        <v>-1.0692</v>
       </c>
       <c r="E40" t="n">
         <v>-1.5696</v>
@@ -2296,7 +2296,7 @@
         <v>-0.7102000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.9783</v>
+        <v>-1.9794</v>
       </c>
       <c r="E41" t="n">
         <v>-3.8541</v>

--- a/database/event/2567/event_2567_evp_summary.xlsx
+++ b/database/event/2567/event_2567_evp_summary.xlsx
@@ -492,403 +492,403 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.8894</v>
+        <v>5.1504</v>
       </c>
       <c r="C2" t="n">
-        <v>0.901</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>1.504</v>
+        <v>1.6871</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8894</v>
+        <v>5.1504</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3917</v>
+        <v>2.2749</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4977</v>
+        <v>2.8755</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1082</v>
+        <v>2.5289</v>
       </c>
       <c r="I2" t="n">
-        <v>4.1403</v>
+        <v>1.3149</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4977</v>
+        <v>2.8755</v>
       </c>
       <c r="K2" t="n">
-        <v>183</v>
+        <v>71</v>
       </c>
       <c r="L2" t="n">
-        <v>105</v>
+        <v>161</v>
       </c>
       <c r="M2" t="n">
-        <v>4.638</v>
+        <v>4.1904</v>
       </c>
       <c r="N2" t="n">
-        <v>288</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.7545</v>
+        <v>4.7952</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8761</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4503</v>
+        <v>1.5268</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7545</v>
+        <v>4.7952</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4613</v>
+        <v>4.3513</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2932</v>
+        <v>0.4439</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4613</v>
+        <v>9.844900000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1844</v>
+        <v>5.1189</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2932</v>
+        <v>0.4439</v>
       </c>
       <c r="K3" t="n">
-        <v>71</v>
+        <v>183</v>
       </c>
       <c r="L3" t="n">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="M3" t="n">
-        <v>4.4776</v>
+        <v>5.5628</v>
       </c>
       <c r="N3" t="n">
-        <v>232</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.0708</v>
+        <v>4.3155</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7501</v>
+        <v>0.7952</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1779</v>
+        <v>1.3102</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0708</v>
+        <v>4.3155</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4882</v>
+        <v>2.3016</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5826</v>
+        <v>2.0139</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4882</v>
+        <v>2.6231</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8273</v>
+        <v>1.3639</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5826</v>
+        <v>2.0139</v>
       </c>
       <c r="K4" t="n">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="L4" t="n">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4099</v>
+        <v>3.3778</v>
       </c>
       <c r="N4" t="n">
-        <v>221</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.9038</v>
+        <v>3.9665</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7194</v>
+        <v>0.7309</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1114</v>
+        <v>1.1527</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9038</v>
+        <v>3.9665</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6297</v>
+        <v>3.3631</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2741</v>
+        <v>0.6034</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6297</v>
+        <v>6.3633</v>
       </c>
       <c r="I5" t="n">
-        <v>2.942</v>
+        <v>3.3086</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2741</v>
+        <v>0.6034</v>
       </c>
       <c r="K5" t="n">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L5" t="n">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2161</v>
+        <v>3.912</v>
       </c>
       <c r="N5" t="n">
-        <v>288</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8848</v>
+        <v>3.824</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7159</v>
+        <v>0.7047</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1038</v>
+        <v>1.0883</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8848</v>
+        <v>3.824</v>
       </c>
       <c r="F6" t="n">
-        <v>3.455</v>
+        <v>2.2963</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4298</v>
+        <v>1.5277</v>
       </c>
       <c r="H6" t="n">
-        <v>3.455</v>
+        <v>2.6045</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8004</v>
+        <v>1.3542</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4298</v>
+        <v>1.5277</v>
       </c>
       <c r="K6" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="L6" t="n">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2302</v>
+        <v>2.8819</v>
       </c>
       <c r="N6" t="n">
-        <v>232</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8724</v>
+        <v>3.6209</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7136</v>
+        <v>0.6672</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0989</v>
+        <v>0.9966</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8724</v>
+        <v>3.6209</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5555</v>
+        <v>3.3554</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3169</v>
+        <v>0.2655</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5555</v>
+        <v>6.3359</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2608</v>
+        <v>3.2944</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3169</v>
+        <v>0.2655</v>
       </c>
       <c r="K7" t="n">
-        <v>71</v>
+        <v>183</v>
       </c>
       <c r="L7" t="n">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5777</v>
+        <v>3.5599</v>
       </c>
       <c r="N7" t="n">
-        <v>232</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3933</v>
+        <v>3.3873</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6253</v>
+        <v>0.6242</v>
       </c>
       <c r="D8" t="n">
-        <v>0.908</v>
+        <v>0.8912</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3933</v>
+        <v>3.3873</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5986</v>
+        <v>2.9737</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7947</v>
+        <v>0.4136</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5986</v>
+        <v>4.9913</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2957</v>
+        <v>2.5952</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7947</v>
+        <v>0.4136</v>
       </c>
       <c r="K8" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="L8" t="n">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0904</v>
+        <v>3.0088</v>
       </c>
       <c r="N8" t="n">
-        <v>187</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9979</v>
+        <v>3.2676</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5524</v>
+        <v>0.6021</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7504999999999999</v>
+        <v>0.8371</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9979</v>
+        <v>3.2676</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2515</v>
+        <v>2.315</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2536</v>
+        <v>0.9526</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2515</v>
+        <v>2.6702</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6354</v>
+        <v>1.3884</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2536</v>
+        <v>0.9526</v>
       </c>
       <c r="K9" t="n">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="L9" t="n">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="M9" t="n">
-        <v>2.3818</v>
+        <v>2.341</v>
       </c>
       <c r="N9" t="n">
-        <v>221</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9349</v>
+        <v>3.0508</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.5622</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7254</v>
+        <v>0.7393</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9349</v>
+        <v>3.0508</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7962</v>
+        <v>3.0597</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1387</v>
+        <v>-0.0089</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7962</v>
+        <v>5.2941</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2664</v>
+        <v>2.7527</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1387</v>
+        <v>-0.0089</v>
       </c>
       <c r="K10" t="n">
         <v>140</v>
@@ -897,7 +897,7 @@
         <v>81</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4051</v>
+        <v>2.7438</v>
       </c>
       <c r="N10" t="n">
         <v>221</v>
@@ -906,35 +906,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6071</v>
+        <v>2.9616</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4804</v>
+        <v>0.5457</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5948</v>
+        <v>0.699</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6071</v>
+        <v>2.9616</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6674</v>
+        <v>2.2302</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9397</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6674</v>
+        <v>2.3716</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3515</v>
+        <v>1.2331</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9397</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="K11" t="n">
         <v>50</v>
@@ -943,7 +943,7 @@
         <v>137</v>
       </c>
       <c r="M11" t="n">
-        <v>2.2912</v>
+        <v>1.9645</v>
       </c>
       <c r="N11" t="n">
         <v>187</v>
@@ -952,47 +952,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.2466</v>
+        <v>2.9389</v>
       </c>
       <c r="C12" t="n">
-        <v>0.414</v>
+        <v>0.5416</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4511</v>
+        <v>0.6888</v>
       </c>
       <c r="E12" t="n">
-        <v>2.2466</v>
+        <v>2.9389</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4345</v>
+        <v>2.7844</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8121</v>
+        <v>0.1545</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4345</v>
+        <v>4.3242</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1627</v>
+        <v>2.2484</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8121</v>
+        <v>0.1545</v>
       </c>
       <c r="K12" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="L12" t="n">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="M12" t="n">
-        <v>1.9748</v>
+        <v>2.4029</v>
       </c>
       <c r="N12" t="n">
-        <v>187</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1924</v>
+        <v>2.9203</v>
       </c>
       <c r="C13" t="n">
-        <v>0.404</v>
+        <v>0.5381</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4295</v>
+        <v>0.6804</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1924</v>
+        <v>2.9203</v>
       </c>
       <c r="F13" t="n">
-        <v>1.76</v>
+        <v>2.3918</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4324</v>
+        <v>0.5285</v>
       </c>
       <c r="H13" t="n">
-        <v>1.76</v>
+        <v>2.941</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4265</v>
+        <v>1.5292</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4324</v>
+        <v>0.5285</v>
       </c>
       <c r="K13" t="n">
         <v>71</v>
@@ -1035,7 +1035,7 @@
         <v>161</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8589</v>
+        <v>2.0577</v>
       </c>
       <c r="N13" t="n">
         <v>232</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1003</v>
+        <v>2.8793</v>
       </c>
       <c r="C14" t="n">
-        <v>0.387</v>
+        <v>0.5306</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3928</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1003</v>
+        <v>2.8793</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9874</v>
+        <v>2.6604</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1129</v>
+        <v>0.2189</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9874</v>
+        <v>3.8873</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6109</v>
+        <v>2.0212</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1129</v>
+        <v>0.2189</v>
       </c>
       <c r="K14" t="n">
         <v>140</v>
@@ -1081,7 +1081,7 @@
         <v>81</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7238</v>
+        <v>2.2401</v>
       </c>
       <c r="N14" t="n">
         <v>221</v>
@@ -1090,185 +1090,185 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0193</v>
+        <v>2.6112</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3721</v>
+        <v>0.4812</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3606</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0193</v>
+        <v>2.6112</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0193</v>
+        <v>2.299</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.3122</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0193</v>
+        <v>2.6139</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0193</v>
+        <v>1.3591</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.3122</v>
       </c>
       <c r="K15" t="n">
-        <v>131</v>
+        <v>50</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="M15" t="n">
-        <v>2.0193</v>
+        <v>1.6713</v>
       </c>
       <c r="N15" t="n">
-        <v>131</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.833</v>
+        <v>2.3508</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3378</v>
+        <v>0.4332</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2864</v>
+        <v>0.4233</v>
       </c>
       <c r="E16" t="n">
-        <v>1.833</v>
+        <v>2.3508</v>
       </c>
       <c r="F16" t="n">
-        <v>1.635</v>
+        <v>1.9634</v>
       </c>
       <c r="G16" t="n">
-        <v>0.198</v>
+        <v>0.3874</v>
       </c>
       <c r="H16" t="n">
-        <v>1.635</v>
+        <v>1.9634</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3252</v>
+        <v>1.0209</v>
       </c>
       <c r="J16" t="n">
-        <v>0.198</v>
+        <v>0.3874</v>
       </c>
       <c r="K16" t="n">
-        <v>50</v>
+        <v>183</v>
       </c>
       <c r="L16" t="n">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5232</v>
+        <v>1.4083</v>
       </c>
       <c r="N16" t="n">
-        <v>187</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4298</v>
+        <v>2.2112</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2635</v>
+        <v>0.4075</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1257</v>
+        <v>0.3602</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4298</v>
+        <v>2.2112</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4298</v>
+        <v>2.2112</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4298</v>
+        <v>2.2112</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4298</v>
+        <v>2.2112</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4298</v>
+        <v>2.2112</v>
       </c>
       <c r="N17" t="n">
-        <v>92</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2117</v>
+        <v>1.844</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2233</v>
+        <v>0.3398</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0388</v>
+        <v>0.1945</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2117</v>
+        <v>1.844</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9393</v>
+        <v>2.433</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2724</v>
+        <v>-0.589</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9393</v>
+        <v>3.0862</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7613</v>
+        <v>1.6047</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2724</v>
+        <v>-0.589</v>
       </c>
       <c r="K18" t="n">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L18" t="n">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0337</v>
+        <v>1.0157</v>
       </c>
       <c r="N18" t="n">
-        <v>288</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0411</v>
+        <v>1.4864</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1918</v>
+        <v>0.2739</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0291</v>
+        <v>0.033</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0411</v>
+        <v>1.4864</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0411</v>
+        <v>1.4864</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0411</v>
+        <v>1.4864</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0411</v>
+        <v>1.4864</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0411</v>
+        <v>1.4864</v>
       </c>
       <c r="N19" t="n">
         <v>102</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0167</v>
+        <v>1.4768</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1873</v>
+        <v>0.2721</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0389</v>
+        <v>0.0287</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0167</v>
+        <v>1.4768</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9125</v>
+        <v>1.4768</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8958</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9125</v>
+        <v>1.4768</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5501</v>
+        <v>1.4768</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8958</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="L20" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6543</v>
+        <v>1.4768</v>
       </c>
       <c r="N20" t="n">
-        <v>221</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9524</v>
+        <v>1.1255</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1755</v>
+        <v>0.2074</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0645</v>
+        <v>-0.1299</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9524</v>
+        <v>1.1255</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9524</v>
+        <v>1.1255</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9524</v>
+        <v>1.1255</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9524</v>
+        <v>1.1255</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9524</v>
+        <v>1.1255</v>
       </c>
       <c r="N21" t="n">
         <v>102</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8257</v>
+        <v>1.0512</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1522</v>
+        <v>0.1937</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.115</v>
+        <v>-0.1634</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8257</v>
+        <v>1.0512</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0032</v>
+        <v>0.2633</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8225</v>
+        <v>0.7879</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0032</v>
+        <v>0.2633</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0026</v>
+        <v>0.1369</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8225</v>
+        <v>0.7879</v>
       </c>
       <c r="K22" t="n">
         <v>50</v>
@@ -1449,7 +1449,7 @@
         <v>137</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8251000000000001</v>
+        <v>0.9248000000000001</v>
       </c>
       <c r="N22" t="n">
         <v>187</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5981</v>
+        <v>0.7929</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1102</v>
+        <v>0.1461</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2056</v>
+        <v>-0.2801</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5981</v>
+        <v>0.7929</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5981</v>
+        <v>0.7929</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5981</v>
+        <v>0.7929</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5981</v>
+        <v>0.7929</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5981</v>
+        <v>0.7929</v>
       </c>
       <c r="N23" t="n">
-        <v>92</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5831</v>
+        <v>0.7593</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1074</v>
+        <v>0.1399</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2116</v>
+        <v>-0.2952</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5831</v>
+        <v>0.7593</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5831</v>
+        <v>0.9139</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.1546</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5831</v>
+        <v>0.9139</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5831</v>
+        <v>0.4752</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.1546</v>
       </c>
       <c r="K24" t="n">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5831</v>
+        <v>0.3206</v>
       </c>
       <c r="N24" t="n">
-        <v>131</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0935</v>
+        <v>0.1331</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2417</v>
+        <v>-0.3119</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="N25" t="n">
         <v>131</v>
@@ -1596,262 +1596,262 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1462</v>
+        <v>0.6973</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0269</v>
+        <v>0.1285</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3857</v>
+        <v>-0.3232</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1462</v>
+        <v>0.6973</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1462</v>
+        <v>0.6973</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1462</v>
+        <v>0.6973</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1462</v>
+        <v>0.6973</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1462</v>
+        <v>0.6973</v>
       </c>
       <c r="N26" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3199</v>
+        <v>0.2902</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0589</v>
+        <v>0.0535</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5714</v>
+        <v>-0.507</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3199</v>
+        <v>0.2902</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1732</v>
+        <v>0.2902</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.4931</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1732</v>
+        <v>0.2902</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1404</v>
+        <v>0.2902</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.4931</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>183</v>
+        <v>102</v>
       </c>
       <c r="L27" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3527</v>
+        <v>0.2902</v>
       </c>
       <c r="N27" t="n">
-        <v>288</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yel</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3332</v>
+        <v>0.0386</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0614</v>
+        <v>0.0071</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5767</v>
+        <v>-0.6206</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3332</v>
+        <v>0.0386</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3332</v>
+        <v>0.0386</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3332</v>
+        <v>0.0386</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3332</v>
+        <v>0.0386</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3332</v>
+        <v>0.0386</v>
       </c>
       <c r="N28" t="n">
-        <v>71</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3693</v>
+        <v>-0.0081</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.0015</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.591</v>
+        <v>-0.6417</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3693</v>
+        <v>-0.0081</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3693</v>
+        <v>-0.0081</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3693</v>
+        <v>-0.0081</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3693</v>
+        <v>-0.0081</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3693</v>
+        <v>-0.0081</v>
       </c>
       <c r="N29" t="n">
-        <v>131</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4293</v>
+        <v>-0.0458</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0791</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6149</v>
+        <v>-0.6587</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4293</v>
+        <v>-0.0458</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4293</v>
+        <v>-0.0458</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4293</v>
+        <v>-0.0458</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4293</v>
+        <v>-0.0458</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4293</v>
+        <v>-0.0458</v>
       </c>
       <c r="N30" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4625</v>
+        <v>-0.2191</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0852</v>
+        <v>-0.0404</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6282</v>
+        <v>-0.7369</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4625</v>
+        <v>-0.2191</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4625</v>
+        <v>-0.2191</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4625</v>
+        <v>-0.2191</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4625</v>
+        <v>-0.2191</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4625</v>
+        <v>-0.2191</v>
       </c>
       <c r="N31" t="n">
         <v>92</v>
@@ -1872,124 +1872,124 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>yel</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.579</v>
+        <v>-0.2679</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1067</v>
+        <v>-0.0494</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6746</v>
+        <v>-0.759</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.579</v>
+        <v>-0.2679</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.579</v>
+        <v>-0.2679</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.579</v>
+        <v>-0.2679</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.579</v>
+        <v>-0.2679</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.579</v>
+        <v>-0.2679</v>
       </c>
       <c r="N32" t="n">
-        <v>102</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SHOOWTiME</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6873</v>
+        <v>-0.3095</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1266</v>
+        <v>-0.057</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7177</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6873</v>
+        <v>-0.3095</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6873</v>
+        <v>-0.3095</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6873</v>
+        <v>-0.3095</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6873</v>
+        <v>-0.3095</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6873</v>
+        <v>-0.3095</v>
       </c>
       <c r="N33" t="n">
-        <v>71</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>destiny</t>
+          <t>SHOOWTiME</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.761</v>
+        <v>-0.3476</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1402</v>
+        <v>-0.0641</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7471</v>
+        <v>-0.7949000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.761</v>
+        <v>-0.3476</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.761</v>
+        <v>-0.3476</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.761</v>
+        <v>-0.3476</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.761</v>
+        <v>-0.3476</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.761</v>
+        <v>-0.3476</v>
       </c>
       <c r="N34" t="n">
         <v>71</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8353</v>
+        <v>-0.4524</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1539</v>
+        <v>-0.0834</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.8423</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8353</v>
+        <v>-0.4524</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8353</v>
+        <v>-0.4524</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8353</v>
+        <v>-0.4524</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8353</v>
+        <v>-0.4524</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8353</v>
+        <v>-0.4524</v>
       </c>
       <c r="N35" t="n">
         <v>71</v>
@@ -2056,32 +2056,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8517</v>
+        <v>-0.4725</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1569</v>
+        <v>-0.0871</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7832</v>
+        <v>-0.8512999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8517</v>
+        <v>-0.4725</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8517</v>
+        <v>-0.4725</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8517</v>
+        <v>-0.4725</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8517</v>
+        <v>-0.4725</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8517</v>
+        <v>-0.4725</v>
       </c>
       <c r="N36" t="n">
         <v>92</v>
@@ -2102,185 +2102,185 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>destiny</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1157</v>
+        <v>-0.5718</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2056</v>
+        <v>-0.1054</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8884</v>
+        <v>-0.8962</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1157</v>
+        <v>-0.5718</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1157</v>
+        <v>-0.5718</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1157</v>
+        <v>-0.5718</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1157</v>
+        <v>-0.5718</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1157</v>
+        <v>-0.5718</v>
       </c>
       <c r="N37" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>PKL</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2097</v>
+        <v>-0.9307</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2229</v>
+        <v>-0.1715</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-1.0582</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2097</v>
+        <v>-0.9307</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.8156</v>
+        <v>-0.9307</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.3941</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8156</v>
+        <v>-0.9307</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.6611</v>
+        <v>-0.9307</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.3941</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>71</v>
       </c>
       <c r="L38" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0552</v>
+        <v>-0.9307</v>
       </c>
       <c r="N38" t="n">
-        <v>232</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PKL</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3903</v>
+        <v>-1.0823</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2562</v>
+        <v>-0.1994</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9978</v>
+        <v>-1.1266</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3903</v>
+        <v>-1.0823</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.3903</v>
+        <v>-1.0823</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.3903</v>
+        <v>-1.0823</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.3903</v>
+        <v>-1.0823</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.3903</v>
+        <v>-1.0823</v>
       </c>
       <c r="N39" t="n">
-        <v>71</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.5696</v>
+        <v>-1.2763</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2892</v>
+        <v>-0.2352</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0692</v>
+        <v>-1.2142</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.5696</v>
+        <v>-1.2763</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.5696</v>
+        <v>-1.0112</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-0.2651</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.5696</v>
+        <v>-1.0112</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.5696</v>
+        <v>-0.5258</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-0.2651</v>
       </c>
       <c r="K40" t="n">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.5696</v>
+        <v>-0.7909</v>
       </c>
       <c r="N40" t="n">
-        <v>131</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.8541</v>
+        <v>-4.5097</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7102000000000001</v>
+        <v>-0.831</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.9794</v>
+        <v>-2.6739</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.8541</v>
+        <v>-4.5097</v>
       </c>
       <c r="F41" t="n">
-        <v>-4.0868</v>
+        <v>-4.8223</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2327</v>
+        <v>0.3126</v>
       </c>
       <c r="H41" t="n">
-        <v>-4.0868</v>
+        <v>-4.8223</v>
       </c>
       <c r="I41" t="n">
-        <v>-3.3125</v>
+        <v>-2.5074</v>
       </c>
       <c r="J41" t="n">
-        <v>0.2327</v>
+        <v>0.3126</v>
       </c>
       <c r="K41" t="n">
         <v>183</v>
@@ -2323,7 +2323,7 @@
         <v>105</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.0798</v>
+        <v>-2.1948</v>
       </c>
       <c r="N41" t="n">
         <v>288</v>
@@ -2429,10 +2429,10 @@
         <v>1.13</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3116</v>
+        <v>0.3363</v>
       </c>
       <c r="J2" t="n">
-        <v>8.7248</v>
+        <v>9.416399999999999</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.97</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0343</v>
+        <v>-0.0416</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9604</v>
+        <v>-1.1648</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.88</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2264</v>
+        <v>-0.146</v>
       </c>
       <c r="J4" t="n">
-        <v>-6.3392</v>
+        <v>-4.088</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.84</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2954</v>
+        <v>-0.1875</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.2712</v>
+        <v>-5.25</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.72</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4739</v>
+        <v>-0.3061</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.2692</v>
+        <v>-8.5708</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.53</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3088</v>
+        <v>1.1945</v>
       </c>
       <c r="J7" t="n">
-        <v>36.6464</v>
+        <v>33.446</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.22</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6288</v>
+        <v>0.6192</v>
       </c>
       <c r="J8" t="n">
-        <v>17.6064</v>
+        <v>17.3376</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1416</v>
+        <v>0.1973</v>
       </c>
       <c r="J9" t="n">
-        <v>3.9648</v>
+        <v>5.5244</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1085</v>
+        <v>0.1656</v>
       </c>
       <c r="J10" t="n">
-        <v>3.038</v>
+        <v>4.6368</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.87</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5405</v>
+        <v>-0.4747</v>
       </c>
       <c r="J11" t="n">
-        <v>-15.134</v>
+        <v>-13.2916</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.11</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2509</v>
+        <v>0.2709</v>
       </c>
       <c r="J12" t="n">
-        <v>7.0252</v>
+        <v>7.5852</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2341</v>
+        <v>0.2505</v>
       </c>
       <c r="J13" t="n">
-        <v>6.5548</v>
+        <v>7.014</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1424</v>
+        <v>0.1427</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9872</v>
+        <v>3.9956</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.89</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2397</v>
+        <v>-0.1435</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.7116</v>
+        <v>-4.018</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.77</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4226</v>
+        <v>-0.2669</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.8328</v>
+        <v>-7.4732</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.26</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7469</v>
+        <v>0.726</v>
       </c>
       <c r="J17" t="n">
-        <v>20.9132</v>
+        <v>20.328</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.17</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5177</v>
+        <v>0.5033</v>
       </c>
       <c r="J18" t="n">
-        <v>14.4956</v>
+        <v>14.0924</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.17</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5177</v>
+        <v>0.5033</v>
       </c>
       <c r="J19" t="n">
-        <v>14.4956</v>
+        <v>14.0924</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.12</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3678</v>
+        <v>0.3741</v>
       </c>
       <c r="J20" t="n">
-        <v>10.2984</v>
+        <v>10.4748</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.85</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.521</v>
       </c>
       <c r="J21" t="n">
-        <v>-16.3016</v>
+        <v>-14.588</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.13</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2952</v>
+        <v>0.2453</v>
       </c>
       <c r="J22" t="n">
-        <v>13.8744</v>
+        <v>11.5291</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1355</v>
+        <v>0.097</v>
       </c>
       <c r="J23" t="n">
-        <v>6.3685</v>
+        <v>4.559</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0.03</v>
+        <v>0.006</v>
       </c>
       <c r="J24" t="n">
-        <v>1.41</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.83</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3263</v>
+        <v>-0.203</v>
       </c>
       <c r="J25" t="n">
-        <v>-15.3361</v>
+        <v>-9.541</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.76</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4291</v>
+        <v>-0.2728</v>
       </c>
       <c r="J26" t="n">
-        <v>-20.1677</v>
+        <v>-12.8216</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.32</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5117</v>
+        <v>0.3957</v>
       </c>
       <c r="J27" t="n">
-        <v>24.0499</v>
+        <v>18.5979</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.31</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4987</v>
+        <v>0.3887</v>
       </c>
       <c r="J28" t="n">
-        <v>23.4389</v>
+        <v>18.2689</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.15</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2686</v>
+        <v>0.2283</v>
       </c>
       <c r="J29" t="n">
-        <v>12.6242</v>
+        <v>10.7301</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.97</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1286</v>
+        <v>-0.0606</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.0442</v>
+        <v>-2.8482</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.78</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4324</v>
+        <v>-0.2705</v>
       </c>
       <c r="J31" t="n">
-        <v>-20.3228</v>
+        <v>-12.7135</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.34</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8851</v>
+        <v>0.6589</v>
       </c>
       <c r="J32" t="n">
-        <v>24.7828</v>
+        <v>18.4492</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.33</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8624000000000001</v>
+        <v>0.6455</v>
       </c>
       <c r="J33" t="n">
-        <v>24.1472</v>
+        <v>18.074</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.33</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8624000000000001</v>
+        <v>0.6455</v>
       </c>
       <c r="J34" t="n">
-        <v>24.1472</v>
+        <v>18.074</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.09</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2079</v>
+        <v>0.2745</v>
       </c>
       <c r="J35" t="n">
-        <v>5.8212</v>
+        <v>7.686</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.9</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4756</v>
+        <v>-0.403</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.3168</v>
+        <v>-11.284</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.16</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3453</v>
+        <v>0.3629</v>
       </c>
       <c r="J37" t="n">
-        <v>9.6684</v>
+        <v>10.1612</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.04</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1396</v>
+        <v>0.1294</v>
       </c>
       <c r="J38" t="n">
-        <v>3.9088</v>
+        <v>3.6232</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.02</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0955</v>
+        <v>0.078</v>
       </c>
       <c r="J39" t="n">
-        <v>2.674</v>
+        <v>2.184</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.75</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4407</v>
+        <v>-0.2814</v>
       </c>
       <c r="J40" t="n">
-        <v>-12.3396</v>
+        <v>-7.8792</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4546</v>
+        <v>-0.2911</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.7288</v>
+        <v>-8.1508</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.31</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8923</v>
+        <v>0.6481</v>
       </c>
       <c r="J42" t="n">
-        <v>26.769</v>
+        <v>19.443</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.14</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4702</v>
+        <v>0.3963</v>
       </c>
       <c r="J43" t="n">
-        <v>14.106</v>
+        <v>11.889</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.08</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2864</v>
+        <v>0.2735</v>
       </c>
       <c r="J44" t="n">
-        <v>8.592000000000001</v>
+        <v>8.205</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.99</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1186</v>
+        <v>-0.0678</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.558</v>
+        <v>-2.034</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.79</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7147</v>
+        <v>-0.6652</v>
       </c>
       <c r="J46" t="n">
-        <v>-21.441</v>
+        <v>-19.956</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.21</v>
       </c>
       <c r="I47" t="n">
-        <v>0.38</v>
+        <v>0.3973</v>
       </c>
       <c r="J47" t="n">
-        <v>11.4</v>
+        <v>11.919</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.09</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1886</v>
+        <v>0.215</v>
       </c>
       <c r="J48" t="n">
-        <v>5.658</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.03</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0557</v>
+        <v>0.0851</v>
       </c>
       <c r="J49" t="n">
-        <v>1.671</v>
+        <v>2.553</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.98</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.09</v>
+        <v>-0.0408</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.7</v>
+        <v>-1.224</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.95</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1536</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>-4.608</v>
+        <v>-2.436</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.05</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1441</v>
+        <v>0.1099</v>
       </c>
       <c r="J52" t="n">
-        <v>4.323</v>
+        <v>3.297</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.03</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1019</v>
+        <v>0.0732</v>
       </c>
       <c r="J53" t="n">
-        <v>3.057</v>
+        <v>2.196</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.02</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0784</v>
+        <v>0.0532</v>
       </c>
       <c r="J54" t="n">
-        <v>2.352</v>
+        <v>1.596</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.98</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0526</v>
+        <v>-0.0346</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.578</v>
+        <v>-1.038</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.82</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3493</v>
+        <v>-0.2165</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.479</v>
+        <v>-6.495</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.39</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5979</v>
+        <v>0.4431</v>
       </c>
       <c r="J57" t="n">
-        <v>17.937</v>
+        <v>13.293</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.27</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4436</v>
+        <v>0.3597</v>
       </c>
       <c r="J58" t="n">
-        <v>13.308</v>
+        <v>10.791</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.13</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2315</v>
+        <v>0.2015</v>
       </c>
       <c r="J59" t="n">
-        <v>6.945</v>
+        <v>6.045</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1884</v>
+        <v>-0.0999</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.652</v>
+        <v>-2.997</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.83</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3635</v>
+        <v>-0.221</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.905</v>
+        <v>-6.63</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.67</v>
       </c>
       <c r="I62" t="n">
-        <v>1.4758</v>
+        <v>1.0417</v>
       </c>
       <c r="J62" t="n">
-        <v>32.4676</v>
+        <v>22.9174</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.5</v>
       </c>
       <c r="I63" t="n">
-        <v>1.1453</v>
+        <v>0.8364</v>
       </c>
       <c r="J63" t="n">
-        <v>25.1966</v>
+        <v>18.4008</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.27</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.5472</v>
       </c>
       <c r="J64" t="n">
-        <v>13.1846</v>
+        <v>12.0384</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.24</v>
       </c>
       <c r="I65" t="n">
-        <v>0.528</v>
+        <v>0.5059</v>
       </c>
       <c r="J65" t="n">
-        <v>11.616</v>
+        <v>11.1298</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.11</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2028</v>
+        <v>0.294</v>
       </c>
       <c r="J66" t="n">
-        <v>4.4616</v>
+        <v>6.468</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.85</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.2</v>
+        <v>-0.1635</v>
       </c>
       <c r="J67" t="n">
-        <v>-4.4</v>
+        <v>-3.597</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.78</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.3313</v>
+        <v>-0.2328</v>
       </c>
       <c r="J68" t="n">
-        <v>-7.2886</v>
+        <v>-5.1216</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.78</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3313</v>
+        <v>-0.2328</v>
       </c>
       <c r="J69" t="n">
-        <v>-7.2886</v>
+        <v>-5.1216</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.76</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3687</v>
+        <v>-0.2514</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.1114</v>
+        <v>-5.5308</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.75</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3857</v>
+        <v>-0.2609</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.4854</v>
+        <v>-5.7398</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.3</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8416</v>
+        <v>0.6217</v>
       </c>
       <c r="J72" t="n">
-        <v>24.4064</v>
+        <v>18.0293</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.19</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5729</v>
+        <v>0.4639</v>
       </c>
       <c r="J73" t="n">
-        <v>16.6141</v>
+        <v>13.4531</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.14</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4334</v>
+        <v>0.3886</v>
       </c>
       <c r="J74" t="n">
-        <v>12.5686</v>
+        <v>11.2694</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.02</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0171</v>
+        <v>0.0696</v>
       </c>
       <c r="J75" t="n">
-        <v>0.4959</v>
+        <v>2.0184</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.91</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4184</v>
+        <v>-0.3512</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.1336</v>
+        <v>-10.1848</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.31</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5077</v>
+        <v>0.4951</v>
       </c>
       <c r="J77" t="n">
-        <v>14.7233</v>
+        <v>14.3579</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.26</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4412</v>
+        <v>0.4449</v>
       </c>
       <c r="J78" t="n">
-        <v>12.7948</v>
+        <v>12.9021</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.11</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2127</v>
+        <v>0.2502</v>
       </c>
       <c r="J79" t="n">
-        <v>6.1683</v>
+        <v>7.2558</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.99</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0735</v>
+        <v>-0.0277</v>
       </c>
       <c r="J80" t="n">
-        <v>-2.1315</v>
+        <v>-0.8033</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.72</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5074</v>
+        <v>-0.3256</v>
       </c>
       <c r="J81" t="n">
-        <v>-14.7146</v>
+        <v>-9.442399999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.2</v>
       </c>
       <c r="I82" t="n">
-        <v>0.402</v>
+        <v>0.4569</v>
       </c>
       <c r="J82" t="n">
-        <v>11.256</v>
+        <v>12.7932</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.96</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.078</v>
+        <v>-0.0593</v>
       </c>
       <c r="J83" t="n">
-        <v>-2.184</v>
+        <v>-1.6604</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.95</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1025</v>
+        <v>-0.0716</v>
       </c>
       <c r="J84" t="n">
-        <v>-2.87</v>
+        <v>-2.0048</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.9</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2089</v>
+        <v>-0.1286</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.8492</v>
+        <v>-3.6008</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.73</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4697</v>
+        <v>-0.3015</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.1516</v>
+        <v>-8.442</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.48</v>
       </c>
       <c r="I87" t="n">
-        <v>1.175</v>
+        <v>1.1125</v>
       </c>
       <c r="J87" t="n">
-        <v>32.9</v>
+        <v>31.15</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.34</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8763</v>
+        <v>0.8807</v>
       </c>
       <c r="J88" t="n">
-        <v>24.5364</v>
+        <v>24.6596</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.27</v>
       </c>
       <c r="I89" t="n">
-        <v>0.7108</v>
+        <v>0.7208</v>
       </c>
       <c r="J89" t="n">
-        <v>19.9024</v>
+        <v>20.1824</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.06</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1097</v>
+        <v>0.1807</v>
       </c>
       <c r="J90" t="n">
-        <v>3.0716</v>
+        <v>5.0596</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.92</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4239</v>
+        <v>-0.3479</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.8692</v>
+        <v>-9.741199999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.33</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4982</v>
+        <v>0.4351</v>
       </c>
       <c r="J92" t="n">
-        <v>13.9496</v>
+        <v>12.1828</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.32</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4851</v>
+        <v>0.4236</v>
       </c>
       <c r="J93" t="n">
-        <v>13.5828</v>
+        <v>11.8608</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.31</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4719</v>
+        <v>0.4121</v>
       </c>
       <c r="J94" t="n">
-        <v>13.2132</v>
+        <v>11.5388</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.16</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2374</v>
+        <v>0.2336</v>
       </c>
       <c r="J95" t="n">
-        <v>6.6472</v>
+        <v>6.5408</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.83</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3764</v>
+        <v>-0.2287</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.5392</v>
+        <v>-6.4036</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.25</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4654</v>
+        <v>0.4146</v>
       </c>
       <c r="J97" t="n">
-        <v>13.0312</v>
+        <v>11.6088</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2409</v>
+        <v>0.1955</v>
       </c>
       <c r="J98" t="n">
-        <v>6.7452</v>
+        <v>5.474</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.02</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0849</v>
+        <v>0.0554</v>
       </c>
       <c r="J99" t="n">
-        <v>2.3772</v>
+        <v>1.5512</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.74</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4601</v>
+        <v>-0.294</v>
       </c>
       <c r="J100" t="n">
-        <v>-12.8828</v>
+        <v>-8.231999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.72</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4872</v>
+        <v>-0.3132</v>
       </c>
       <c r="J101" t="n">
-        <v>-13.6416</v>
+        <v>-8.769600000000001</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.23</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4817</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J102" t="n">
-        <v>12.5242</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0692</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.7992</v>
+        <v>-1.8694</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.79</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3516</v>
+        <v>-0.2303</v>
       </c>
       <c r="J104" t="n">
-        <v>-9.1416</v>
+        <v>-5.9878</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.65</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5536</v>
+        <v>-0.3646</v>
       </c>
       <c r="J105" t="n">
-        <v>-14.3936</v>
+        <v>-9.4796</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.63</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.3834</v>
       </c>
       <c r="J106" t="n">
-        <v>-15.0826</v>
+        <v>-9.968400000000001</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.7</v>
       </c>
       <c r="I107" t="n">
-        <v>1.5949</v>
+        <v>1.387</v>
       </c>
       <c r="J107" t="n">
-        <v>41.4674</v>
+        <v>36.062</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.57</v>
       </c>
       <c r="I108" t="n">
-        <v>1.351</v>
+        <v>1.2257</v>
       </c>
       <c r="J108" t="n">
-        <v>35.126</v>
+        <v>31.8682</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.18</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4494</v>
+        <v>0.5092</v>
       </c>
       <c r="J109" t="n">
-        <v>11.6844</v>
+        <v>13.2392</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.05</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0761</v>
+        <v>0.1479</v>
       </c>
       <c r="J110" t="n">
-        <v>1.9786</v>
+        <v>3.8454</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.59</v>
       </c>
       <c r="I111" t="n">
-        <v>-1.187</v>
+        <v>-1.188</v>
       </c>
       <c r="J111" t="n">
-        <v>-30.862</v>
+        <v>-30.888</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.68</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.3174</v>
+        <v>-0.2697</v>
       </c>
       <c r="J112" t="n">
-        <v>-5.7132</v>
+        <v>-4.8546</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.59</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.4561</v>
+        <v>-0.3644</v>
       </c>
       <c r="J113" t="n">
-        <v>-8.2098</v>
+        <v>-6.5592</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.46</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.6938</v>
+        <v>-0.4845</v>
       </c>
       <c r="J114" t="n">
-        <v>-12.4884</v>
+        <v>-8.721</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.45</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.7095</v>
+        <v>-0.4939</v>
       </c>
       <c r="J115" t="n">
-        <v>-12.771</v>
+        <v>-8.8902</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.38</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.8125</v>
+        <v>-0.5615</v>
       </c>
       <c r="J116" t="n">
-        <v>-14.625</v>
+        <v>-10.107</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.84</v>
       </c>
       <c r="I117" t="n">
-        <v>1.7131</v>
+        <v>1.4802</v>
       </c>
       <c r="J117" t="n">
-        <v>30.8358</v>
+        <v>26.6436</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.76</v>
       </c>
       <c r="I118" t="n">
-        <v>1.571</v>
+        <v>1.3899</v>
       </c>
       <c r="J118" t="n">
-        <v>28.278</v>
+        <v>25.0182</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.76</v>
       </c>
       <c r="I119" t="n">
-        <v>1.571</v>
+        <v>1.3899</v>
       </c>
       <c r="J119" t="n">
-        <v>28.278</v>
+        <v>25.0182</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.25</v>
       </c>
       <c r="I120" t="n">
-        <v>0.4946</v>
+        <v>0.6158</v>
       </c>
       <c r="J120" t="n">
-        <v>8.902799999999999</v>
+        <v>11.0844</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2072</v>
+        <v>-0.1191</v>
       </c>
       <c r="J121" t="n">
-        <v>-3.7296</v>
+        <v>-2.1438</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.28</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4899</v>
+        <v>0.5778</v>
       </c>
       <c r="J122" t="n">
-        <v>13.2273</v>
+        <v>15.6006</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.12</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2568</v>
+        <v>0.2835</v>
       </c>
       <c r="J123" t="n">
-        <v>6.9336</v>
+        <v>7.6545</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.95</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1401</v>
+        <v>-0.0771</v>
       </c>
       <c r="J124" t="n">
-        <v>-3.7827</v>
+        <v>-2.0817</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.88</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2648</v>
+        <v>-0.1575</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.1496</v>
+        <v>-4.2525</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.83</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3425</v>
+        <v>-0.21</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.2475</v>
+        <v>-5.67</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.49</v>
       </c>
       <c r="I127" t="n">
-        <v>1.2448</v>
+        <v>1.1514</v>
       </c>
       <c r="J127" t="n">
-        <v>33.6096</v>
+        <v>31.0878</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.4</v>
       </c>
       <c r="I128" t="n">
-        <v>1.0594</v>
+        <v>1.0292</v>
       </c>
       <c r="J128" t="n">
-        <v>28.6038</v>
+        <v>27.7884</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3606</v>
+        <v>-0.292</v>
       </c>
       <c r="J129" t="n">
-        <v>-9.7362</v>
+        <v>-7.884</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.9</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4484</v>
+        <v>-0.3816</v>
       </c>
       <c r="J130" t="n">
-        <v>-12.1068</v>
+        <v>-10.3032</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.86</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5569</v>
+        <v>-0.4943</v>
       </c>
       <c r="J131" t="n">
-        <v>-15.0363</v>
+        <v>-13.3461</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.26</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4768</v>
+        <v>0.5574</v>
       </c>
       <c r="J132" t="n">
-        <v>13.8272</v>
+        <v>16.1646</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.01</v>
       </c>
       <c r="I133" t="n">
-        <v>0.056</v>
+        <v>0.0423</v>
       </c>
       <c r="J133" t="n">
-        <v>1.624</v>
+        <v>1.2267</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.02</v>
+        <v>0.0039</v>
       </c>
       <c r="J134" t="n">
-        <v>0.58</v>
+        <v>0.1131</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.91</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2006</v>
+        <v>-0.12</v>
       </c>
       <c r="J135" t="n">
-        <v>-5.8174</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.68</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5411</v>
+        <v>-0.3519</v>
       </c>
       <c r="J136" t="n">
-        <v>-15.6919</v>
+        <v>-10.2051</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.59</v>
       </c>
       <c r="I137" t="n">
-        <v>1.423</v>
+        <v>1.2704</v>
       </c>
       <c r="J137" t="n">
-        <v>41.267</v>
+        <v>36.8416</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.43</v>
       </c>
       <c r="I138" t="n">
-        <v>1.1046</v>
+        <v>1.0627</v>
       </c>
       <c r="J138" t="n">
-        <v>32.0334</v>
+        <v>30.8183</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.11</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2945</v>
+        <v>0.3415</v>
       </c>
       <c r="J139" t="n">
-        <v>8.5405</v>
+        <v>9.903499999999999</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.92</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4032</v>
+        <v>-0.3316</v>
       </c>
       <c r="J140" t="n">
-        <v>-11.6928</v>
+        <v>-9.616400000000001</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.7</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.9449</v>
+        <v>-0.9132</v>
       </c>
       <c r="J141" t="n">
-        <v>-27.4021</v>
+        <v>-26.4828</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.85</v>
       </c>
       <c r="I142" t="n">
-        <v>1.0235</v>
+        <v>0.9422</v>
       </c>
       <c r="J142" t="n">
-        <v>21.4935</v>
+        <v>19.7862</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.56</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7168</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="J143" t="n">
-        <v>15.0528</v>
+        <v>13.7277</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.32</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4005</v>
+        <v>0.4029</v>
       </c>
       <c r="J144" t="n">
-        <v>8.410500000000001</v>
+        <v>8.460900000000001</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.22</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2672</v>
+        <v>0.2864</v>
       </c>
       <c r="J145" t="n">
-        <v>5.6112</v>
+        <v>6.0144</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.04</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.0074</v>
+        <v>0.0368</v>
       </c>
       <c r="J146" t="n">
-        <v>-0.1554</v>
+        <v>0.7728</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.25</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5316</v>
       </c>
       <c r="J147" t="n">
-        <v>11.928</v>
+        <v>11.1636</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.22</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5263</v>
+        <v>0.4849</v>
       </c>
       <c r="J148" t="n">
-        <v>11.0523</v>
+        <v>10.1829</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.53</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.6766</v>
+        <v>-0.457</v>
       </c>
       <c r="J149" t="n">
-        <v>-14.2086</v>
+        <v>-9.597</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.37</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.8763</v>
+        <v>-0.606</v>
       </c>
       <c r="J150" t="n">
-        <v>-18.4023</v>
+        <v>-12.726</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.2</v>
       </c>
       <c r="I151" t="n">
-        <v>-1.0714</v>
+        <v>-0.7631</v>
       </c>
       <c r="J151" t="n">
-        <v>-22.4994</v>
+        <v>-16.0251</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.44</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7379</v>
+        <v>0.9216</v>
       </c>
       <c r="J152" t="n">
-        <v>18.4475</v>
+        <v>23.04</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.9</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1607</v>
+        <v>-0.1225</v>
       </c>
       <c r="J153" t="n">
-        <v>-4.0175</v>
+        <v>-3.0625</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.78</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3787</v>
+        <v>-0.2439</v>
       </c>
       <c r="J154" t="n">
-        <v>-9.467499999999999</v>
+        <v>-6.0975</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.76</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4085</v>
+        <v>-0.2635</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.2125</v>
+        <v>-6.5875</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.51</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.7359</v>
+        <v>-0.4979</v>
       </c>
       <c r="J156" t="n">
-        <v>-18.3975</v>
+        <v>-12.4475</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>2.02</v>
       </c>
       <c r="I157" t="n">
-        <v>2.0342</v>
+        <v>1.7497</v>
       </c>
       <c r="J157" t="n">
-        <v>50.855</v>
+        <v>43.7425</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.28</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6875</v>
+        <v>0.7321</v>
       </c>
       <c r="J158" t="n">
-        <v>17.1875</v>
+        <v>18.3025</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.22</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5192</v>
+        <v>0.5949</v>
       </c>
       <c r="J159" t="n">
-        <v>12.98</v>
+        <v>14.8725</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.17</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3909</v>
+        <v>0.4719</v>
       </c>
       <c r="J160" t="n">
-        <v>9.772500000000001</v>
+        <v>11.7975</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.9908</v>
+        <v>-0.9644</v>
       </c>
       <c r="J161" t="n">
-        <v>-24.77</v>
+        <v>-24.11</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.11</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2764</v>
+        <v>0.2923</v>
       </c>
       <c r="J162" t="n">
-        <v>7.1864</v>
+        <v>7.5998</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.98</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0147</v>
+        <v>-0.0283</v>
       </c>
       <c r="J163" t="n">
-        <v>-0.3822</v>
+        <v>-0.7358</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.96</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0602</v>
+        <v>-0.0561</v>
       </c>
       <c r="J164" t="n">
-        <v>-1.5652</v>
+        <v>-1.4586</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.79</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.376</v>
+        <v>-0.2388</v>
       </c>
       <c r="J165" t="n">
-        <v>-9.776</v>
+        <v>-6.2088</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.74</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4481</v>
+        <v>-0.2878</v>
       </c>
       <c r="J166" t="n">
-        <v>-11.6506</v>
+        <v>-7.4828</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.42</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0921</v>
+        <v>1.0533</v>
       </c>
       <c r="J167" t="n">
-        <v>28.3946</v>
+        <v>27.3858</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.19</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5581</v>
+        <v>0.5486</v>
       </c>
       <c r="J168" t="n">
-        <v>14.5106</v>
+        <v>14.2636</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.04</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0804</v>
+        <v>0.1356</v>
       </c>
       <c r="J169" t="n">
-        <v>2.0904</v>
+        <v>3.5256</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.04</v>
       </c>
       <c r="I170" t="n">
-        <v>0.0804</v>
+        <v>0.1356</v>
       </c>
       <c r="J170" t="n">
-        <v>2.0904</v>
+        <v>3.5256</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.98</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.198</v>
+        <v>-0.1277</v>
       </c>
       <c r="J171" t="n">
-        <v>-5.148</v>
+        <v>-3.3202</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.08</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2828</v>
+        <v>0.2914</v>
       </c>
       <c r="J172" t="n">
-        <v>5.9388</v>
+        <v>6.1194</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1061</v>
+        <v>0.0689</v>
       </c>
       <c r="J173" t="n">
-        <v>2.2281</v>
+        <v>1.4469</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.67</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.5037</v>
+        <v>-0.3351</v>
       </c>
       <c r="J174" t="n">
-        <v>-10.5777</v>
+        <v>-7.0371</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.66</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.5181</v>
+        <v>-0.3446</v>
       </c>
       <c r="J175" t="n">
-        <v>-10.8801</v>
+        <v>-7.2366</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.46</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.7786</v>
+        <v>-0.5308</v>
       </c>
       <c r="J176" t="n">
-        <v>-16.3506</v>
+        <v>-11.1468</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.47</v>
       </c>
       <c r="I177" t="n">
-        <v>1.0931</v>
+        <v>1.0763</v>
       </c>
       <c r="J177" t="n">
-        <v>22.9551</v>
+        <v>22.6023</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.45</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0509</v>
+        <v>1.051</v>
       </c>
       <c r="J178" t="n">
-        <v>22.0689</v>
+        <v>22.071</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.33</v>
       </c>
       <c r="I179" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.8329</v>
       </c>
       <c r="J179" t="n">
-        <v>15.9516</v>
+        <v>17.4909</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.3</v>
       </c>
       <c r="I180" t="n">
-        <v>0.6825</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="J180" t="n">
-        <v>14.3325</v>
+        <v>16.1196</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.14</v>
       </c>
       <c r="I181" t="n">
-        <v>0.2886</v>
+        <v>0.3801</v>
       </c>
       <c r="J181" t="n">
-        <v>6.0606</v>
+        <v>7.9821</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.44</v>
       </c>
       <c r="I182" t="n">
-        <v>1.0636</v>
+        <v>1.049</v>
       </c>
       <c r="J182" t="n">
-        <v>24.4628</v>
+        <v>24.127</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.4</v>
       </c>
       <c r="I183" t="n">
-        <v>0.978</v>
+        <v>0.9877</v>
       </c>
       <c r="J183" t="n">
-        <v>22.494</v>
+        <v>22.7171</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.24</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5735</v>
+        <v>0.6428</v>
       </c>
       <c r="J184" t="n">
-        <v>13.1905</v>
+        <v>14.7844</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.18</v>
       </c>
       <c r="I185" t="n">
-        <v>0.4187</v>
+        <v>0.498</v>
       </c>
       <c r="J185" t="n">
-        <v>9.630100000000001</v>
+        <v>11.454</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.1</v>
       </c>
       <c r="I186" t="n">
-        <v>0.205</v>
+        <v>0.2856</v>
       </c>
       <c r="J186" t="n">
-        <v>4.715</v>
+        <v>6.5688</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.3</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5717</v>
+        <v>0.6853</v>
       </c>
       <c r="J187" t="n">
-        <v>13.1491</v>
+        <v>15.7619</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.79</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.3558</v>
+        <v>-0.2315</v>
       </c>
       <c r="J188" t="n">
-        <v>-8.183400000000001</v>
+        <v>-5.3245</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.79</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3558</v>
+        <v>-0.2315</v>
       </c>
       <c r="J189" t="n">
-        <v>-8.183400000000001</v>
+        <v>-5.3245</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.72</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4601</v>
+        <v>-0.2995</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.5823</v>
+        <v>-6.8885</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5021</v>
+        <v>-0.3281</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.5483</v>
+        <v>-7.5463</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.06</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3178</v>
+        <v>0.3516</v>
       </c>
       <c r="J192" t="n">
-        <v>7.3094</v>
+        <v>8.0868</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.71</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.3421</v>
+        <v>-0.2757</v>
       </c>
       <c r="J193" t="n">
-        <v>-7.8683</v>
+        <v>-6.3411</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.64</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.4584</v>
+        <v>-0.3425</v>
       </c>
       <c r="J194" t="n">
-        <v>-10.5432</v>
+        <v>-7.8775</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.46</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.7438</v>
+        <v>-0.508</v>
       </c>
       <c r="J195" t="n">
-        <v>-17.1074</v>
+        <v>-11.684</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.27</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.9817</v>
+        <v>-0.6887</v>
       </c>
       <c r="J196" t="n">
-        <v>-22.5791</v>
+        <v>-15.8401</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>2.17</v>
       </c>
       <c r="I197" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J197" t="n">
-        <v>47.3639</v>
+        <v>42.1774</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.44</v>
       </c>
       <c r="I198" t="n">
-        <v>0.9203</v>
+        <v>1.0205</v>
       </c>
       <c r="J198" t="n">
-        <v>21.1669</v>
+        <v>23.4715</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.35</v>
       </c>
       <c r="I199" t="n">
-        <v>0.7245</v>
+        <v>0.8497</v>
       </c>
       <c r="J199" t="n">
-        <v>16.6635</v>
+        <v>19.5431</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.32</v>
       </c>
       <c r="I200" t="n">
-        <v>0.6592</v>
+        <v>0.7832</v>
       </c>
       <c r="J200" t="n">
-        <v>15.1616</v>
+        <v>18.0136</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.17</v>
       </c>
       <c r="I201" t="n">
-        <v>0.3177</v>
+        <v>0.4258</v>
       </c>
       <c r="J201" t="n">
-        <v>7.3071</v>
+        <v>9.7934</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.14</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3402</v>
+        <v>0.3706</v>
       </c>
       <c r="J202" t="n">
-        <v>8.8452</v>
+        <v>9.6356</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.92</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.12</v>
+        <v>-0.0997</v>
       </c>
       <c r="J203" t="n">
-        <v>-3.12</v>
+        <v>-2.5922</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.89</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1778</v>
+        <v>-0.1329</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.6228</v>
+        <v>-3.4554</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.78</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3773</v>
+        <v>-0.2434</v>
       </c>
       <c r="J205" t="n">
-        <v>-9.809799999999999</v>
+        <v>-6.3284</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.64</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.573</v>
+        <v>-0.3775</v>
       </c>
       <c r="J206" t="n">
-        <v>-14.898</v>
+        <v>-9.815</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.47</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1526</v>
+        <v>1.0988</v>
       </c>
       <c r="J207" t="n">
-        <v>29.9676</v>
+        <v>28.5688</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.44</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0908</v>
+        <v>1.06</v>
       </c>
       <c r="J208" t="n">
-        <v>28.3608</v>
+        <v>27.56</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.35</v>
       </c>
       <c r="I209" t="n">
-        <v>0.8966</v>
+        <v>0.9019</v>
       </c>
       <c r="J209" t="n">
-        <v>23.3116</v>
+        <v>23.4494</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1298</v>
+        <v>-0.0531</v>
       </c>
       <c r="J210" t="n">
-        <v>-3.3748</v>
+        <v>-1.3806</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.83</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6622</v>
+        <v>-0.601</v>
       </c>
       <c r="J211" t="n">
-        <v>-17.2172</v>
+        <v>-15.626</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.33</v>
       </c>
       <c r="I212" t="n">
-        <v>0.9117</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="J212" t="n">
-        <v>43.7616</v>
+        <v>42.9456</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.24</v>
       </c>
       <c r="I213" t="n">
-        <v>0.702</v>
+        <v>0.6795</v>
       </c>
       <c r="J213" t="n">
-        <v>33.696</v>
+        <v>32.616</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.2</v>
       </c>
       <c r="I214" t="n">
-        <v>0.6016</v>
+        <v>0.5807</v>
       </c>
       <c r="J214" t="n">
-        <v>28.8768</v>
+        <v>27.8736</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.09</v>
       </c>
       <c r="I215" t="n">
-        <v>0.2641</v>
+        <v>0.2944</v>
       </c>
       <c r="J215" t="n">
-        <v>12.6768</v>
+        <v>14.1312</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.68</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.9788</v>
+        <v>-0.9516</v>
       </c>
       <c r="J216" t="n">
-        <v>-46.9824</v>
+        <v>-45.6768</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.18</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3572</v>
+        <v>0.4042</v>
       </c>
       <c r="J217" t="n">
-        <v>17.1456</v>
+        <v>19.4016</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.18</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3572</v>
+        <v>0.4042</v>
       </c>
       <c r="J218" t="n">
-        <v>17.1456</v>
+        <v>19.4016</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.93</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1714</v>
+        <v>-0.0992</v>
       </c>
       <c r="J219" t="n">
-        <v>-8.2272</v>
+        <v>-4.7616</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.93</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1714</v>
+        <v>-0.0992</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.2272</v>
+        <v>-4.7616</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.74</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4656</v>
+        <v>-0.2971</v>
       </c>
       <c r="J221" t="n">
-        <v>-22.3488</v>
+        <v>-14.2608</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.44</v>
       </c>
       <c r="I222" t="n">
-        <v>1.1202</v>
+        <v>1.0735</v>
       </c>
       <c r="J222" t="n">
-        <v>30.2454</v>
+        <v>28.9845</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.27</v>
       </c>
       <c r="I223" t="n">
-        <v>0.744</v>
+        <v>0.7351</v>
       </c>
       <c r="J223" t="n">
-        <v>20.088</v>
+        <v>19.8477</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.12</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3177</v>
+        <v>0.3665</v>
       </c>
       <c r="J224" t="n">
-        <v>8.5779</v>
+        <v>9.8955</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.11</v>
       </c>
       <c r="I225" t="n">
-        <v>0.2879</v>
+        <v>0.3394</v>
       </c>
       <c r="J225" t="n">
-        <v>7.7733</v>
+        <v>9.1638</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.86</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5709</v>
+        <v>-0.5059</v>
       </c>
       <c r="J226" t="n">
-        <v>-15.4143</v>
+        <v>-13.6593</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.41</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6566</v>
+        <v>0.8028</v>
       </c>
       <c r="J227" t="n">
-        <v>17.7282</v>
+        <v>21.6756</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.01</v>
       </c>
       <c r="I228" t="n">
-        <v>0.0375</v>
+        <v>0.0372</v>
       </c>
       <c r="J228" t="n">
-        <v>1.0125</v>
+        <v>1.0044</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.93</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1758</v>
+        <v>-0.1005</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.7466</v>
+        <v>-2.7135</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.91</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2119</v>
+        <v>-0.1235</v>
       </c>
       <c r="J230" t="n">
-        <v>-5.7213</v>
+        <v>-3.3345</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.76</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4408</v>
+        <v>-0.279</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.9016</v>
+        <v>-7.533</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.91</v>
       </c>
       <c r="I232" t="n">
-        <v>1.8467</v>
+        <v>1.5657</v>
       </c>
       <c r="J232" t="n">
-        <v>44.3208</v>
+        <v>37.5768</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.87</v>
       </c>
       <c r="I233" t="n">
-        <v>1.7795</v>
+        <v>1.5208</v>
       </c>
       <c r="J233" t="n">
-        <v>42.708</v>
+        <v>36.4992</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.35</v>
       </c>
       <c r="I234" t="n">
-        <v>0.726</v>
+        <v>0.8505</v>
       </c>
       <c r="J234" t="n">
-        <v>17.424</v>
+        <v>20.412</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.17</v>
       </c>
       <c r="I235" t="n">
-        <v>0.3187</v>
+        <v>0.4266</v>
       </c>
       <c r="J235" t="n">
-        <v>7.6488</v>
+        <v>10.2384</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.13</v>
       </c>
       <c r="I236" t="n">
-        <v>0.2197</v>
+        <v>0.3216</v>
       </c>
       <c r="J236" t="n">
-        <v>5.2728</v>
+        <v>7.7184</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>0.96</v>
       </c>
       <c r="I237" t="n">
-        <v>0.0323</v>
+        <v>-0.0127</v>
       </c>
       <c r="J237" t="n">
-        <v>0.7752</v>
+        <v>-0.3048</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.72</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.3791</v>
+        <v>-0.2807</v>
       </c>
       <c r="J238" t="n">
-        <v>-9.0984</v>
+        <v>-6.7368</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.7</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.4241</v>
+        <v>-0.2983</v>
       </c>
       <c r="J239" t="n">
-        <v>-10.1784</v>
+        <v>-7.1592</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.59</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5941</v>
+        <v>-0.4002</v>
       </c>
       <c r="J240" t="n">
-        <v>-14.2584</v>
+        <v>-9.604799999999999</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.58</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.608</v>
+        <v>-0.4096</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.592</v>
+        <v>-9.830399999999999</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2567/event_2567_evp_summary.xlsx
+++ b/database/event/2567/event_2567_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.1504</v>
+        <v>5.1591</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.9507</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6871</v>
+        <v>1.7243</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1504</v>
+        <v>5.1591</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2749</v>
+        <v>2.1987</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8755</v>
+        <v>2.9604</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5289</v>
+        <v>2.36</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3149</v>
+        <v>1.2744</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8755</v>
+        <v>2.9604</v>
       </c>
       <c r="K2" t="n">
         <v>71</v>
@@ -529,7 +529,7 @@
         <v>161</v>
       </c>
       <c r="M2" t="n">
-        <v>4.1904</v>
+        <v>4.2348</v>
       </c>
       <c r="N2" t="n">
         <v>232</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.7952</v>
+        <v>4.7561</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.8764</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5268</v>
+        <v>1.5409</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7952</v>
+        <v>4.7561</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3513</v>
+        <v>4.2686</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4439</v>
+        <v>0.4875</v>
       </c>
       <c r="H3" t="n">
-        <v>9.844900000000001</v>
+        <v>9.189399999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1189</v>
+        <v>4.9622</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4439</v>
+        <v>0.4875</v>
       </c>
       <c r="K3" t="n">
         <v>183</v>
@@ -575,7 +575,7 @@
         <v>105</v>
       </c>
       <c r="M3" t="n">
-        <v>5.5628</v>
+        <v>5.4497</v>
       </c>
       <c r="N3" t="n">
         <v>288</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.3155</v>
+        <v>4.3285</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7952</v>
+        <v>0.7976</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3102</v>
+        <v>1.3462</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3155</v>
+        <v>4.3285</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3016</v>
+        <v>2.2208</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0139</v>
+        <v>2.1077</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6231</v>
+        <v>2.4332</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3639</v>
+        <v>1.3139</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0139</v>
+        <v>2.1077</v>
       </c>
       <c r="K4" t="n">
         <v>71</v>
@@ -621,7 +621,7 @@
         <v>161</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3778</v>
+        <v>3.4216</v>
       </c>
       <c r="N4" t="n">
         <v>232</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.9665</v>
+        <v>3.9513</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7309</v>
+        <v>0.7281</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1527</v>
+        <v>1.1745</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9665</v>
+        <v>3.9513</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3631</v>
+        <v>3.279</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6034</v>
+        <v>0.6723</v>
       </c>
       <c r="H5" t="n">
-        <v>6.3633</v>
+        <v>5.9245</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3086</v>
+        <v>3.1992</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6034</v>
+        <v>0.6723</v>
       </c>
       <c r="K5" t="n">
         <v>140</v>
@@ -667,7 +667,7 @@
         <v>81</v>
       </c>
       <c r="M5" t="n">
-        <v>3.912</v>
+        <v>3.8715</v>
       </c>
       <c r="N5" t="n">
         <v>221</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.824</v>
+        <v>3.8555</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7047</v>
+        <v>0.7105</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0883</v>
+        <v>1.1309</v>
       </c>
       <c r="E6" t="n">
-        <v>3.824</v>
+        <v>3.8555</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2963</v>
+        <v>2.2135</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5277</v>
+        <v>1.642</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6045</v>
+        <v>2.4091</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3542</v>
+        <v>1.3009</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5277</v>
+        <v>1.642</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
@@ -713,7 +713,7 @@
         <v>137</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8819</v>
+        <v>2.9429</v>
       </c>
       <c r="N6" t="n">
         <v>187</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6209</v>
+        <v>3.5464</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6672</v>
+        <v>0.6535</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9966</v>
+        <v>0.9902</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6209</v>
+        <v>3.5464</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3554</v>
+        <v>3.2668</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2655</v>
+        <v>0.2796</v>
       </c>
       <c r="H7" t="n">
-        <v>6.3359</v>
+        <v>5.8842</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2944</v>
+        <v>3.1774</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2655</v>
+        <v>0.2796</v>
       </c>
       <c r="K7" t="n">
         <v>183</v>
@@ -759,7 +759,7 @@
         <v>105</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5599</v>
+        <v>3.457</v>
       </c>
       <c r="N7" t="n">
         <v>288</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3873</v>
+        <v>3.5431</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6242</v>
+        <v>0.6529</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8912</v>
+        <v>0.9887</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3873</v>
+        <v>3.5431</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9737</v>
+        <v>2.9995</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4136</v>
+        <v>0.5436</v>
       </c>
       <c r="H8" t="n">
-        <v>4.9913</v>
+        <v>5.0021</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5952</v>
+        <v>2.7011</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4136</v>
+        <v>0.5436</v>
       </c>
       <c r="K8" t="n">
         <v>71</v>
@@ -805,7 +805,7 @@
         <v>161</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0088</v>
+        <v>3.2447</v>
       </c>
       <c r="N8" t="n">
         <v>232</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2676</v>
+        <v>3.241</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6021</v>
+        <v>0.5972</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8371</v>
+        <v>0.8512</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2676</v>
+        <v>3.241</v>
       </c>
       <c r="F9" t="n">
-        <v>2.315</v>
+        <v>2.2382</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9526</v>
+        <v>1.0028</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6702</v>
+        <v>2.4904</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3884</v>
+        <v>1.3448</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9526</v>
+        <v>1.0028</v>
       </c>
       <c r="K9" t="n">
         <v>50</v>
@@ -851,7 +851,7 @@
         <v>137</v>
       </c>
       <c r="M9" t="n">
-        <v>2.341</v>
+        <v>2.3476</v>
       </c>
       <c r="N9" t="n">
         <v>187</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0508</v>
+        <v>3.0082</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5622</v>
+        <v>0.5543</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7393</v>
+        <v>0.7452</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0508</v>
+        <v>3.0082</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0597</v>
+        <v>2.9966</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0089</v>
+        <v>0.0116</v>
       </c>
       <c r="H10" t="n">
-        <v>5.2941</v>
+        <v>4.9927</v>
       </c>
       <c r="I10" t="n">
-        <v>2.7527</v>
+        <v>2.696</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0089</v>
+        <v>0.0116</v>
       </c>
       <c r="K10" t="n">
         <v>140</v>
@@ -897,7 +897,7 @@
         <v>81</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7438</v>
+        <v>2.7076</v>
       </c>
       <c r="N10" t="n">
         <v>221</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9616</v>
+        <v>2.9839</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5457</v>
+        <v>0.5498</v>
       </c>
       <c r="D11" t="n">
-        <v>0.699</v>
+        <v>0.7341</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9616</v>
+        <v>2.9839</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2302</v>
+        <v>2.1521</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.8318</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3716</v>
+        <v>2.2063</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2331</v>
+        <v>1.1914</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.8318</v>
       </c>
       <c r="K11" t="n">
         <v>50</v>
@@ -943,7 +943,7 @@
         <v>137</v>
       </c>
       <c r="M11" t="n">
-        <v>1.9645</v>
+        <v>2.0232</v>
       </c>
       <c r="N11" t="n">
         <v>187</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9389</v>
+        <v>2.9264</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5416</v>
+        <v>0.5392</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6888</v>
+        <v>0.708</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9389</v>
+        <v>2.9264</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7844</v>
+        <v>2.7349</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1545</v>
+        <v>0.1915</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3242</v>
+        <v>4.1293</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2484</v>
+        <v>2.2298</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1545</v>
+        <v>0.1915</v>
       </c>
       <c r="K12" t="n">
         <v>140</v>
@@ -989,7 +989,7 @@
         <v>81</v>
       </c>
       <c r="M12" t="n">
-        <v>2.4029</v>
+        <v>2.4213</v>
       </c>
       <c r="N12" t="n">
         <v>221</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9203</v>
+        <v>2.8269</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5381</v>
+        <v>0.5209</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6804</v>
+        <v>0.6627</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9203</v>
+        <v>2.8269</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3918</v>
+        <v>2.303</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5285</v>
+        <v>0.5239</v>
       </c>
       <c r="H13" t="n">
-        <v>2.941</v>
+        <v>2.7041</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5292</v>
+        <v>1.4602</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5285</v>
+        <v>0.5239</v>
       </c>
       <c r="K13" t="n">
         <v>71</v>
@@ -1035,7 +1035,7 @@
         <v>161</v>
       </c>
       <c r="M13" t="n">
-        <v>2.0577</v>
+        <v>1.9841</v>
       </c>
       <c r="N13" t="n">
         <v>232</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.8793</v>
+        <v>2.7901</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5306</v>
+        <v>0.5141</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.6459</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8793</v>
+        <v>2.7901</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6604</v>
+        <v>2.5643</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2189</v>
+        <v>0.2258</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8873</v>
+        <v>3.5665</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0212</v>
+        <v>1.9259</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2189</v>
+        <v>0.2258</v>
       </c>
       <c r="K14" t="n">
         <v>140</v>
@@ -1081,7 +1081,7 @@
         <v>81</v>
       </c>
       <c r="M14" t="n">
-        <v>2.2401</v>
+        <v>2.1517</v>
       </c>
       <c r="N14" t="n">
         <v>221</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6112</v>
+        <v>2.6129</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4812</v>
+        <v>0.4815</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.5652</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6112</v>
+        <v>2.6129</v>
       </c>
       <c r="F15" t="n">
-        <v>2.299</v>
+        <v>2.227</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3122</v>
+        <v>0.3859</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6139</v>
+        <v>2.4536</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3591</v>
+        <v>1.3249</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3122</v>
+        <v>0.3859</v>
       </c>
       <c r="K15" t="n">
         <v>50</v>
@@ -1127,7 +1127,7 @@
         <v>137</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6713</v>
+        <v>1.7108</v>
       </c>
       <c r="N15" t="n">
         <v>187</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3508</v>
+        <v>2.3036</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4332</v>
+        <v>0.4245</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4233</v>
+        <v>0.4244</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3508</v>
+        <v>2.3036</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9634</v>
+        <v>1.8967</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3874</v>
+        <v>0.4069</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9634</v>
+        <v>1.8967</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0209</v>
+        <v>1.0242</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3874</v>
+        <v>0.4069</v>
       </c>
       <c r="K16" t="n">
         <v>183</v>
@@ -1173,7 +1173,7 @@
         <v>105</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4083</v>
+        <v>1.4311</v>
       </c>
       <c r="N16" t="n">
         <v>288</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2112</v>
+        <v>2.1323</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4075</v>
+        <v>0.3929</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3602</v>
+        <v>0.3465</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2112</v>
+        <v>2.1323</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2112</v>
+        <v>2.1323</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2112</v>
+        <v>2.1323</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2112</v>
+        <v>2.1323</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.2112</v>
+        <v>2.1323</v>
       </c>
       <c r="N17" t="n">
         <v>131</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.844</v>
+        <v>1.7671</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3398</v>
+        <v>0.3256</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1945</v>
+        <v>0.1802</v>
       </c>
       <c r="E18" t="n">
-        <v>1.844</v>
+        <v>1.7671</v>
       </c>
       <c r="F18" t="n">
-        <v>2.433</v>
+        <v>2.3937</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.589</v>
+        <v>-0.6266</v>
       </c>
       <c r="H18" t="n">
-        <v>3.0862</v>
+        <v>3.0034</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6047</v>
+        <v>1.6218</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.589</v>
+        <v>-0.6266</v>
       </c>
       <c r="K18" t="n">
         <v>140</v>
@@ -1265,7 +1265,7 @@
         <v>81</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0157</v>
+        <v>0.9951999999999999</v>
       </c>
       <c r="N18" t="n">
         <v>221</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4864</v>
+        <v>1.4186</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2739</v>
+        <v>0.2614</v>
       </c>
       <c r="D19" t="n">
-        <v>0.033</v>
+        <v>0.0216</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4864</v>
+        <v>1.4186</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4864</v>
+        <v>1.4186</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4864</v>
+        <v>1.4186</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4864</v>
+        <v>1.4186</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4864</v>
+        <v>1.4186</v>
       </c>
       <c r="N19" t="n">
         <v>102</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4768</v>
+        <v>1.4183</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2721</v>
+        <v>0.2614</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0287</v>
+        <v>0.0214</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4768</v>
+        <v>1.4183</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4768</v>
+        <v>1.4183</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4768</v>
+        <v>1.4183</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4768</v>
+        <v>1.4183</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4768</v>
+        <v>1.4183</v>
       </c>
       <c r="N20" t="n">
         <v>92</v>
@@ -1366,185 +1366,185 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1255</v>
+        <v>1.1611</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2074</v>
+        <v>0.214</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1299</v>
+        <v>-0.0956</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1255</v>
+        <v>1.1611</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1255</v>
+        <v>0.2711</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1255</v>
+        <v>0.2711</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1255</v>
+        <v>0.1464</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="K21" t="n">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1255</v>
+        <v>1.0364</v>
       </c>
       <c r="N21" t="n">
-        <v>102</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0512</v>
+        <v>1.0943</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1937</v>
+        <v>0.2016</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1634</v>
+        <v>-0.1261</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0512</v>
+        <v>1.0943</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2633</v>
+        <v>1.0943</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7879</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2633</v>
+        <v>1.0943</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1369</v>
+        <v>1.0943</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7879</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="L22" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9248000000000001</v>
+        <v>1.0943</v>
       </c>
       <c r="N22" t="n">
-        <v>187</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7929</v>
+        <v>0.772</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1461</v>
+        <v>0.1423</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2801</v>
+        <v>-0.2728</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7929</v>
+        <v>0.772</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7929</v>
+        <v>0.9122</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.1402</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7929</v>
+        <v>0.9122</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7929</v>
+        <v>0.4926</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.1402</v>
       </c>
       <c r="K23" t="n">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7929</v>
+        <v>0.3524</v>
       </c>
       <c r="N23" t="n">
-        <v>131</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7593</v>
+        <v>0.7084</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1399</v>
+        <v>0.1305</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2952</v>
+        <v>-0.3017</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7593</v>
+        <v>0.7084</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9139</v>
+        <v>0.7084</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1546</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9139</v>
+        <v>0.7084</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4752</v>
+        <v>0.7084</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1546</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>183</v>
+        <v>131</v>
       </c>
       <c r="L24" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3206</v>
+        <v>0.7084</v>
       </c>
       <c r="N24" t="n">
-        <v>288</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.6929</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1331</v>
+        <v>0.1277</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3119</v>
+        <v>-0.3088</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.6929</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.6929</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.6929</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.6929</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.6929</v>
       </c>
       <c r="N25" t="n">
         <v>131</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6973</v>
+        <v>0.6552</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1285</v>
+        <v>0.1207</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3232</v>
+        <v>-0.3259</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6973</v>
+        <v>0.6552</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6973</v>
+        <v>0.6552</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6973</v>
+        <v>0.6552</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6973</v>
+        <v>0.6552</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6973</v>
+        <v>0.6552</v>
       </c>
       <c r="N26" t="n">
         <v>92</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2902</v>
+        <v>0.2654</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0535</v>
+        <v>0.0489</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.507</v>
+        <v>-0.5034</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2902</v>
+        <v>0.2654</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2902</v>
+        <v>0.2654</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2902</v>
+        <v>0.2654</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2902</v>
+        <v>0.2654</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2902</v>
+        <v>0.2654</v>
       </c>
       <c r="N27" t="n">
         <v>102</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0386</v>
+        <v>-0.0532</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0071</v>
+        <v>-0.0098</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6206</v>
+        <v>-0.6484</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0386</v>
+        <v>-0.0532</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0386</v>
+        <v>-0.0532</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0386</v>
+        <v>-0.0532</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0386</v>
+        <v>-0.0532</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0386</v>
+        <v>-0.0532</v>
       </c>
       <c r="N28" t="n">
-        <v>131</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0081</v>
+        <v>-0.061</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0015</v>
+        <v>-0.0112</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6417</v>
+        <v>-0.652</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0081</v>
+        <v>-0.061</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0081</v>
+        <v>-0.061</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0081</v>
+        <v>-0.061</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0081</v>
+        <v>-0.061</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0081</v>
+        <v>-0.061</v>
       </c>
       <c r="N29" t="n">
-        <v>102</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0458</v>
+        <v>-0.0905</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0167</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6587</v>
+        <v>-0.6654</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0458</v>
+        <v>-0.0905</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0458</v>
+        <v>-0.0905</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0458</v>
+        <v>-0.0905</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0458</v>
+        <v>-0.0905</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0458</v>
+        <v>-0.0905</v>
       </c>
       <c r="N30" t="n">
         <v>92</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2191</v>
+        <v>-0.2938</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0404</v>
+        <v>-0.0541</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7369</v>
+        <v>-0.7579</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2191</v>
+        <v>-0.2938</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2191</v>
+        <v>-0.2938</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2191</v>
+        <v>-0.2938</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2191</v>
+        <v>-0.2938</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2191</v>
+        <v>-0.2938</v>
       </c>
       <c r="N31" t="n">
         <v>92</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yel</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2679</v>
+        <v>-0.3118</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0494</v>
+        <v>-0.0575</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.759</v>
+        <v>-0.7661</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2679</v>
+        <v>-0.3118</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2679</v>
+        <v>-0.3118</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.2679</v>
+        <v>-0.3118</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2679</v>
+        <v>-0.3118</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2679</v>
+        <v>-0.3118</v>
       </c>
       <c r="N32" t="n">
-        <v>71</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>yel</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3095</v>
+        <v>-0.3179</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.057</v>
+        <v>-0.0586</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.7689</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3095</v>
+        <v>-0.3179</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3095</v>
+        <v>-0.3179</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3095</v>
+        <v>-0.3179</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3095</v>
+        <v>-0.3179</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3095</v>
+        <v>-0.3179</v>
       </c>
       <c r="N33" t="n">
-        <v>102</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3476</v>
+        <v>-0.3946</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0641</v>
+        <v>-0.0727</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-0.8038</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3476</v>
+        <v>-0.3946</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3476</v>
+        <v>-0.3946</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3476</v>
+        <v>-0.3946</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3476</v>
+        <v>-0.3946</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3476</v>
+        <v>-0.3946</v>
       </c>
       <c r="N34" t="n">
         <v>71</v>
@@ -2010,93 +2010,93 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>shz</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4524</v>
+        <v>-0.4699</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0834</v>
+        <v>-0.0866</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8423</v>
+        <v>-0.8381</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.4524</v>
+        <v>-0.4699</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.4524</v>
+        <v>-0.4699</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.4524</v>
+        <v>-0.4699</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4524</v>
+        <v>-0.4699</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.4524</v>
+        <v>-0.4699</v>
       </c>
       <c r="N35" t="n">
-        <v>71</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>shz</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.4725</v>
+        <v>-0.4862</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0871</v>
+        <v>-0.0896</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8512999999999999</v>
+        <v>-0.8455</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.4725</v>
+        <v>-0.4862</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4725</v>
+        <v>-0.4862</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4725</v>
+        <v>-0.4862</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4725</v>
+        <v>-0.4862</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.4725</v>
+        <v>-0.4862</v>
       </c>
       <c r="N36" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.5718</v>
+        <v>-0.6075</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1054</v>
+        <v>-0.1119</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8962</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.5718</v>
+        <v>-0.6075</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.5718</v>
+        <v>-0.6075</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.5718</v>
+        <v>-0.6075</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.5718</v>
+        <v>-0.6075</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.5718</v>
+        <v>-0.6075</v>
       </c>
       <c r="N37" t="n">
         <v>71</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9307</v>
+        <v>-0.9818</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1715</v>
+        <v>-0.1809</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0582</v>
+        <v>-1.0711</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9307</v>
+        <v>-0.9818</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9307</v>
+        <v>-0.9818</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9307</v>
+        <v>-0.9818</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9307</v>
+        <v>-0.9818</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9307</v>
+        <v>-0.9818</v>
       </c>
       <c r="N38" t="n">
         <v>71</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0823</v>
+        <v>-0.9993</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1994</v>
+        <v>-0.1841</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1266</v>
+        <v>-1.0791</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0823</v>
+        <v>-0.9993</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0823</v>
+        <v>-0.8061</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.1932</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0823</v>
+        <v>-0.8061</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0823</v>
+        <v>-0.4353</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.1932</v>
       </c>
       <c r="K39" t="n">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0823</v>
+        <v>-0.6285000000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>131</v>
+        <v>232</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2763</v>
+        <v>-1.0712</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2352</v>
+        <v>-0.1974</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2142</v>
+        <v>-1.1118</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2763</v>
+        <v>-1.0712</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.0112</v>
+        <v>-1.0712</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.2651</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.0112</v>
+        <v>-1.0712</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5258</v>
+        <v>-1.0712</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.2651</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="L40" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.7909</v>
+        <v>-1.0712</v>
       </c>
       <c r="N40" t="n">
-        <v>232</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.5097</v>
+        <v>-4.009</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.831</v>
+        <v>-0.7387</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.6739</v>
+        <v>-2.4492</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.5097</v>
+        <v>-4.009</v>
       </c>
       <c r="F41" t="n">
-        <v>-4.8223</v>
+        <v>-4.3628</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3126</v>
+        <v>0.3538</v>
       </c>
       <c r="H41" t="n">
-        <v>-4.8223</v>
+        <v>-4.3628</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.5074</v>
+        <v>-2.3559</v>
       </c>
       <c r="J41" t="n">
-        <v>0.3126</v>
+        <v>0.3538</v>
       </c>
       <c r="K41" t="n">
         <v>183</v>
@@ -2323,7 +2323,7 @@
         <v>105</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.1948</v>
+        <v>-2.0021</v>
       </c>
       <c r="N41" t="n">
         <v>288</v>
@@ -2429,10 +2429,10 @@
         <v>1.13</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3363</v>
+        <v>0.3316</v>
       </c>
       <c r="J2" t="n">
-        <v>9.416399999999999</v>
+        <v>9.284800000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.97</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0416</v>
+        <v>-0.0518</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.1648</v>
+        <v>-1.4504</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.88</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.146</v>
+        <v>-0.1615</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.088</v>
+        <v>-4.522</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.84</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1875</v>
+        <v>-0.2035</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.25</v>
+        <v>-5.698</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.72</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3061</v>
+        <v>-0.3204</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.5708</v>
+        <v>-8.9712</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.53</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1945</v>
+        <v>1.2127</v>
       </c>
       <c r="J7" t="n">
-        <v>33.446</v>
+        <v>33.9556</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.22</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6192</v>
+        <v>0.5958</v>
       </c>
       <c r="J8" t="n">
-        <v>17.3376</v>
+        <v>16.6824</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1973</v>
+        <v>0.2088</v>
       </c>
       <c r="J9" t="n">
-        <v>5.5244</v>
+        <v>5.8464</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1656</v>
+        <v>0.1787</v>
       </c>
       <c r="J10" t="n">
-        <v>4.6368</v>
+        <v>5.0036</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.87</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4747</v>
+        <v>-0.448</v>
       </c>
       <c r="J11" t="n">
-        <v>-13.2916</v>
+        <v>-12.544</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.11</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2709</v>
+        <v>0.275</v>
       </c>
       <c r="J12" t="n">
-        <v>7.5852</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2505</v>
+        <v>0.2555</v>
       </c>
       <c r="J13" t="n">
-        <v>7.014</v>
+        <v>7.154</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1427</v>
+        <v>0.1503</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9956</v>
+        <v>4.2084</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.89</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1435</v>
+        <v>-0.1568</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.018</v>
+        <v>-4.3904</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.77</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2669</v>
+        <v>-0.2803</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.4732</v>
+        <v>-7.8484</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.26</v>
       </c>
       <c r="I17" t="n">
-        <v>0.726</v>
+        <v>0.6886</v>
       </c>
       <c r="J17" t="n">
-        <v>20.328</v>
+        <v>19.2808</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.17</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5033</v>
+        <v>0.4902</v>
       </c>
       <c r="J18" t="n">
-        <v>14.0924</v>
+        <v>13.7256</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.17</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5033</v>
+        <v>0.4902</v>
       </c>
       <c r="J19" t="n">
-        <v>14.0924</v>
+        <v>13.7256</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.12</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3741</v>
+        <v>0.3722</v>
       </c>
       <c r="J20" t="n">
-        <v>10.4748</v>
+        <v>10.4216</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.85</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.521</v>
+        <v>-0.4917</v>
       </c>
       <c r="J21" t="n">
-        <v>-14.588</v>
+        <v>-13.7676</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.13</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2453</v>
+        <v>0.2507</v>
       </c>
       <c r="J22" t="n">
-        <v>11.5291</v>
+        <v>11.7829</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>0.097</v>
+        <v>0.1036</v>
       </c>
       <c r="J23" t="n">
-        <v>4.559</v>
+        <v>4.8692</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0.006</v>
+        <v>0.0043</v>
       </c>
       <c r="J24" t="n">
-        <v>0.282</v>
+        <v>0.2021</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.83</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.203</v>
+        <v>-0.2178</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.541</v>
+        <v>-10.2366</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.76</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2728</v>
+        <v>-0.2869</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.8216</v>
+        <v>-13.4843</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.32</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3957</v>
+        <v>0.4435</v>
       </c>
       <c r="J27" t="n">
-        <v>18.5979</v>
+        <v>20.8445</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.31</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3887</v>
+        <v>0.4339</v>
       </c>
       <c r="J28" t="n">
-        <v>18.2689</v>
+        <v>20.3933</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.15</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2283</v>
+        <v>0.2441</v>
       </c>
       <c r="J29" t="n">
-        <v>10.7301</v>
+        <v>11.4727</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.97</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0606</v>
+        <v>-0.0664</v>
       </c>
       <c r="J30" t="n">
-        <v>-2.8482</v>
+        <v>-3.1208</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.78</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2705</v>
+        <v>-0.2811</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.7135</v>
+        <v>-13.2117</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.34</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6589</v>
+        <v>0.7306</v>
       </c>
       <c r="J32" t="n">
-        <v>18.4492</v>
+        <v>20.4568</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.33</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6455</v>
+        <v>0.7159</v>
       </c>
       <c r="J33" t="n">
-        <v>18.074</v>
+        <v>20.0452</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.33</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6455</v>
+        <v>0.7159</v>
       </c>
       <c r="J34" t="n">
-        <v>18.074</v>
+        <v>20.0452</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.09</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2745</v>
+        <v>0.2841</v>
       </c>
       <c r="J35" t="n">
-        <v>7.686</v>
+        <v>7.9548</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.9</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.403</v>
+        <v>-0.3798</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.284</v>
+        <v>-10.6344</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.16</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3629</v>
+        <v>0.378</v>
       </c>
       <c r="J37" t="n">
-        <v>10.1612</v>
+        <v>10.584</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.04</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1294</v>
+        <v>0.1342</v>
       </c>
       <c r="J38" t="n">
-        <v>3.6232</v>
+        <v>3.7576</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.02</v>
       </c>
       <c r="I39" t="n">
-        <v>0.078</v>
+        <v>0.0819</v>
       </c>
       <c r="J39" t="n">
-        <v>2.184</v>
+        <v>2.2932</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.75</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2814</v>
+        <v>-0.2955</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.8792</v>
+        <v>-8.273999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2911</v>
+        <v>-0.305</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.1508</v>
+        <v>-8.539999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.31</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6481</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>19.443</v>
+        <v>21.366</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.14</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3963</v>
+        <v>0.4276</v>
       </c>
       <c r="J43" t="n">
-        <v>11.889</v>
+        <v>12.828</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.08</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2735</v>
+        <v>0.2762</v>
       </c>
       <c r="J44" t="n">
-        <v>8.205</v>
+        <v>8.286</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.99</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0678</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>-2.034</v>
+        <v>-2.058</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.79</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6652</v>
+        <v>-0.6231</v>
       </c>
       <c r="J46" t="n">
-        <v>-19.956</v>
+        <v>-18.693</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.21</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3973</v>
+        <v>0.4364</v>
       </c>
       <c r="J47" t="n">
-        <v>11.919</v>
+        <v>13.092</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.09</v>
       </c>
       <c r="I48" t="n">
-        <v>0.215</v>
+        <v>0.2249</v>
       </c>
       <c r="J48" t="n">
-        <v>6.45</v>
+        <v>6.747</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.03</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0851</v>
+        <v>0.0953</v>
       </c>
       <c r="J49" t="n">
-        <v>2.553</v>
+        <v>2.859</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.98</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0408</v>
+        <v>-0.0464</v>
       </c>
       <c r="J50" t="n">
-        <v>-1.224</v>
+        <v>-1.392</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.95</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.0902</v>
       </c>
       <c r="J51" t="n">
-        <v>-2.436</v>
+        <v>-2.706</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.05</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1099</v>
+        <v>0.1182</v>
       </c>
       <c r="J52" t="n">
-        <v>3.297</v>
+        <v>3.546</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.03</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0732</v>
+        <v>0.0804</v>
       </c>
       <c r="J53" t="n">
-        <v>2.196</v>
+        <v>2.412</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.02</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0532</v>
+        <v>0.0594</v>
       </c>
       <c r="J54" t="n">
-        <v>1.596</v>
+        <v>1.782</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.98</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0346</v>
+        <v>-0.0417</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.038</v>
+        <v>-1.251</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.82</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2165</v>
+        <v>-0.2306</v>
       </c>
       <c r="J56" t="n">
-        <v>-6.495</v>
+        <v>-6.918</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.39</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4431</v>
+        <v>0.5018</v>
       </c>
       <c r="J57" t="n">
-        <v>13.293</v>
+        <v>15.054</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.27</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3597</v>
+        <v>0.3896</v>
       </c>
       <c r="J58" t="n">
-        <v>10.791</v>
+        <v>11.688</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.13</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2015</v>
+        <v>0.2176</v>
       </c>
       <c r="J59" t="n">
-        <v>6.045</v>
+        <v>6.528</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0999</v>
+        <v>-0.1081</v>
       </c>
       <c r="J60" t="n">
-        <v>-2.997</v>
+        <v>-3.243</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.83</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.221</v>
+        <v>-0.2318</v>
       </c>
       <c r="J61" t="n">
-        <v>-6.63</v>
+        <v>-6.954</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.67</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0417</v>
+        <v>1.1494</v>
       </c>
       <c r="J62" t="n">
-        <v>22.9174</v>
+        <v>25.2868</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.5</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8364</v>
+        <v>0.9295</v>
       </c>
       <c r="J63" t="n">
-        <v>18.4008</v>
+        <v>20.449</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.27</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5472</v>
+        <v>0.6116</v>
       </c>
       <c r="J64" t="n">
-        <v>12.0384</v>
+        <v>13.4552</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.24</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5059</v>
+        <v>0.5655</v>
       </c>
       <c r="J65" t="n">
-        <v>11.1298</v>
+        <v>12.441</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.11</v>
       </c>
       <c r="I66" t="n">
-        <v>0.294</v>
+        <v>0.3107</v>
       </c>
       <c r="J66" t="n">
-        <v>6.468</v>
+        <v>6.8354</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.85</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.1635</v>
+        <v>-0.1827</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.597</v>
+        <v>-4.0194</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.78</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2328</v>
+        <v>-0.2518</v>
       </c>
       <c r="J68" t="n">
-        <v>-5.1216</v>
+        <v>-5.5396</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.78</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2328</v>
+        <v>-0.2518</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.1216</v>
+        <v>-5.5396</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.76</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2514</v>
+        <v>-0.2703</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.5308</v>
+        <v>-5.9466</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.75</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2609</v>
+        <v>-0.2796</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.7398</v>
+        <v>-6.1512</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.3</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6217</v>
+        <v>0.6859</v>
       </c>
       <c r="J72" t="n">
-        <v>18.0293</v>
+        <v>19.8911</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.19</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4639</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>13.4531</v>
+        <v>14.8074</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.14</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3886</v>
+        <v>0.4195</v>
       </c>
       <c r="J74" t="n">
-        <v>11.2694</v>
+        <v>12.1655</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.02</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0696</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="J75" t="n">
-        <v>2.0184</v>
+        <v>2.4099</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.91</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3512</v>
+        <v>-0.3371</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.1848</v>
+        <v>-9.7759</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.31</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4951</v>
+        <v>0.553</v>
       </c>
       <c r="J77" t="n">
-        <v>14.3579</v>
+        <v>16.037</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.26</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4449</v>
+        <v>0.4952</v>
       </c>
       <c r="J78" t="n">
-        <v>12.9021</v>
+        <v>14.3608</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.11</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2502</v>
+        <v>0.26</v>
       </c>
       <c r="J79" t="n">
-        <v>7.2558</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.99</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0277</v>
+        <v>-0.0307</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.8033</v>
+        <v>-0.8903</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.72</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3256</v>
+        <v>-0.3358</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.442399999999999</v>
+        <v>-9.738200000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.2</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4569</v>
+        <v>0.4471</v>
       </c>
       <c r="J82" t="n">
-        <v>12.7932</v>
+        <v>12.5188</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.96</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0593</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.6604</v>
+        <v>-1.946</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.95</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.0716</v>
+        <v>-0.0828</v>
       </c>
       <c r="J84" t="n">
-        <v>-2.0048</v>
+        <v>-2.3184</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.9</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1286</v>
+        <v>-0.1426</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.6008</v>
+        <v>-3.9928</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.73</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3015</v>
+        <v>-0.315</v>
       </c>
       <c r="J86" t="n">
-        <v>-8.442</v>
+        <v>-8.82</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.48</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1125</v>
+        <v>1.0736</v>
       </c>
       <c r="J87" t="n">
-        <v>31.15</v>
+        <v>30.0608</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.34</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8807</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="J88" t="n">
-        <v>24.6596</v>
+        <v>23.2428</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.27</v>
       </c>
       <c r="I89" t="n">
-        <v>0.7208</v>
+        <v>0.6895</v>
       </c>
       <c r="J89" t="n">
-        <v>20.1824</v>
+        <v>19.306</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.06</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1807</v>
+        <v>0.1973</v>
       </c>
       <c r="J90" t="n">
-        <v>5.0596</v>
+        <v>5.5244</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.92</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3479</v>
+        <v>-0.328</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.741199999999999</v>
+        <v>-9.183999999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.33</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4351</v>
+        <v>0.4473</v>
       </c>
       <c r="J92" t="n">
-        <v>12.1828</v>
+        <v>12.5244</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.32</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4236</v>
+        <v>0.4363</v>
       </c>
       <c r="J93" t="n">
-        <v>11.8608</v>
+        <v>12.2164</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.31</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4121</v>
+        <v>0.4253</v>
       </c>
       <c r="J94" t="n">
-        <v>11.5388</v>
+        <v>11.9084</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.16</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2336</v>
+        <v>0.2513</v>
       </c>
       <c r="J95" t="n">
-        <v>6.5408</v>
+        <v>7.0364</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.83</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2287</v>
+        <v>-0.2379</v>
       </c>
       <c r="J96" t="n">
-        <v>-6.4036</v>
+        <v>-6.6612</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.25</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4146</v>
+        <v>0.4123</v>
       </c>
       <c r="J97" t="n">
-        <v>11.6088</v>
+        <v>11.5444</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1955</v>
+        <v>0.203</v>
       </c>
       <c r="J98" t="n">
-        <v>5.474</v>
+        <v>5.684</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.02</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0554</v>
+        <v>0.061</v>
       </c>
       <c r="J99" t="n">
-        <v>1.5512</v>
+        <v>1.708</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.74</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.294</v>
+        <v>-0.3073</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.231999999999999</v>
+        <v>-8.6044</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.72</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3132</v>
+        <v>-0.3261</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.769600000000001</v>
+        <v>-9.130800000000001</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.23</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5334</v>
       </c>
       <c r="J102" t="n">
-        <v>14.56</v>
+        <v>13.8684</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.0866</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.8694</v>
+        <v>-2.2516</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.79</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2303</v>
+        <v>-0.2477</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.9878</v>
+        <v>-6.4402</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.65</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3646</v>
+        <v>-0.3784</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.4796</v>
+        <v>-9.8384</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.63</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3834</v>
+        <v>-0.3964</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.968400000000001</v>
+        <v>-10.3064</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.7</v>
       </c>
       <c r="I107" t="n">
-        <v>1.387</v>
+        <v>1.3664</v>
       </c>
       <c r="J107" t="n">
-        <v>36.062</v>
+        <v>35.5264</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.57</v>
       </c>
       <c r="I108" t="n">
-        <v>1.2257</v>
+        <v>1.1952</v>
       </c>
       <c r="J108" t="n">
-        <v>31.8682</v>
+        <v>31.0752</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.18</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5092</v>
+        <v>0.4997</v>
       </c>
       <c r="J109" t="n">
-        <v>13.2392</v>
+        <v>12.9922</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.05</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1479</v>
+        <v>0.1664</v>
       </c>
       <c r="J110" t="n">
-        <v>3.8454</v>
+        <v>4.3264</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.59</v>
       </c>
       <c r="I111" t="n">
-        <v>-1.188</v>
+        <v>-1.0724</v>
       </c>
       <c r="J111" t="n">
-        <v>-30.888</v>
+        <v>-27.8824</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.68</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.2697</v>
+        <v>-0.2995</v>
       </c>
       <c r="J112" t="n">
-        <v>-4.8546</v>
+        <v>-5.391</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.59</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.3644</v>
+        <v>-0.3884</v>
       </c>
       <c r="J113" t="n">
-        <v>-6.5592</v>
+        <v>-6.9912</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.46</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.4845</v>
+        <v>-0.501</v>
       </c>
       <c r="J114" t="n">
-        <v>-8.721</v>
+        <v>-9.018000000000001</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.45</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4939</v>
+        <v>-0.5098</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.8902</v>
+        <v>-9.176399999999999</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.38</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5615</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.107</v>
+        <v>-10.2978</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.84</v>
       </c>
       <c r="I117" t="n">
-        <v>1.4802</v>
+        <v>1.4769</v>
       </c>
       <c r="J117" t="n">
-        <v>26.6436</v>
+        <v>26.5842</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.76</v>
       </c>
       <c r="I118" t="n">
-        <v>1.3899</v>
+        <v>1.3814</v>
       </c>
       <c r="J118" t="n">
-        <v>25.0182</v>
+        <v>24.8652</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.76</v>
       </c>
       <c r="I119" t="n">
-        <v>1.3899</v>
+        <v>1.3814</v>
       </c>
       <c r="J119" t="n">
-        <v>25.0182</v>
+        <v>24.8652</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.25</v>
       </c>
       <c r="I120" t="n">
-        <v>0.6158</v>
+        <v>0.6079</v>
       </c>
       <c r="J120" t="n">
-        <v>11.0844</v>
+        <v>10.9422</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1191</v>
+        <v>-0.083</v>
       </c>
       <c r="J121" t="n">
-        <v>-2.1438</v>
+        <v>-1.494</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.28</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5778</v>
+        <v>0.5624</v>
       </c>
       <c r="J122" t="n">
-        <v>15.6006</v>
+        <v>15.1848</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.12</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2835</v>
+        <v>0.2887</v>
       </c>
       <c r="J123" t="n">
-        <v>7.6545</v>
+        <v>7.7949</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.95</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0771</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="J124" t="n">
-        <v>-2.0817</v>
+        <v>-2.349</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.88</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1575</v>
+        <v>-0.1704</v>
       </c>
       <c r="J125" t="n">
-        <v>-4.2525</v>
+        <v>-4.6008</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.83</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.21</v>
+        <v>-0.2233</v>
       </c>
       <c r="J126" t="n">
-        <v>-5.67</v>
+        <v>-6.0291</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.49</v>
       </c>
       <c r="I127" t="n">
-        <v>1.1514</v>
+        <v>1.1106</v>
       </c>
       <c r="J127" t="n">
-        <v>31.0878</v>
+        <v>29.9862</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.4</v>
       </c>
       <c r="I128" t="n">
-        <v>1.0292</v>
+        <v>0.9707</v>
       </c>
       <c r="J128" t="n">
-        <v>27.7884</v>
+        <v>26.2089</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.292</v>
+        <v>-0.2818</v>
       </c>
       <c r="J129" t="n">
-        <v>-7.884</v>
+        <v>-7.6086</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.9</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3816</v>
+        <v>-0.3648</v>
       </c>
       <c r="J130" t="n">
-        <v>-10.3032</v>
+        <v>-9.849600000000001</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.86</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4943</v>
+        <v>-0.4674</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.3461</v>
+        <v>-12.6198</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.26</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5574</v>
+        <v>0.5411</v>
       </c>
       <c r="J132" t="n">
-        <v>16.1646</v>
+        <v>15.6919</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.01</v>
       </c>
       <c r="I133" t="n">
-        <v>0.0423</v>
+        <v>0.0466</v>
       </c>
       <c r="J133" t="n">
-        <v>1.2267</v>
+        <v>1.3514</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0039</v>
+        <v>0.0027</v>
       </c>
       <c r="J134" t="n">
-        <v>0.1131</v>
+        <v>0.07829999999999999</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.91</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.12</v>
+        <v>-0.1331</v>
       </c>
       <c r="J135" t="n">
-        <v>-3.48</v>
+        <v>-3.8599</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.68</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3519</v>
+        <v>-0.3635</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.2051</v>
+        <v>-10.5415</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.59</v>
       </c>
       <c r="I137" t="n">
-        <v>1.2704</v>
+        <v>1.2393</v>
       </c>
       <c r="J137" t="n">
-        <v>36.8416</v>
+        <v>35.9397</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.43</v>
       </c>
       <c r="I138" t="n">
-        <v>1.0627</v>
+        <v>1.0129</v>
       </c>
       <c r="J138" t="n">
-        <v>30.8183</v>
+        <v>29.3741</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.11</v>
       </c>
       <c r="I139" t="n">
-        <v>0.3415</v>
+        <v>0.3436</v>
       </c>
       <c r="J139" t="n">
-        <v>9.903499999999999</v>
+        <v>9.964399999999999</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.92</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3316</v>
+        <v>-0.3165</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.616400000000001</v>
+        <v>-9.1785</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.7</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.9132</v>
+        <v>-0.8369</v>
       </c>
       <c r="J141" t="n">
-        <v>-26.4828</v>
+        <v>-24.2701</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.85</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9422</v>
+        <v>0.9267</v>
       </c>
       <c r="J142" t="n">
-        <v>19.7862</v>
+        <v>19.4607</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.56</v>
       </c>
       <c r="I143" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6589</v>
       </c>
       <c r="J143" t="n">
-        <v>13.7277</v>
+        <v>13.8369</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.32</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4029</v>
+        <v>0.4208</v>
       </c>
       <c r="J144" t="n">
-        <v>8.460900000000001</v>
+        <v>8.8368</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.22</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2864</v>
+        <v>0.3081</v>
       </c>
       <c r="J145" t="n">
-        <v>6.0144</v>
+        <v>6.4701</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.04</v>
       </c>
       <c r="I146" t="n">
-        <v>0.0368</v>
+        <v>0.0579</v>
       </c>
       <c r="J146" t="n">
-        <v>0.7728</v>
+        <v>1.2159</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.25</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5316</v>
+        <v>0.5011</v>
       </c>
       <c r="J147" t="n">
-        <v>11.1636</v>
+        <v>10.5231</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.22</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4849</v>
+        <v>0.4581</v>
       </c>
       <c r="J148" t="n">
-        <v>10.1829</v>
+        <v>9.620100000000001</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.53</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.457</v>
+        <v>-0.4695</v>
       </c>
       <c r="J149" t="n">
-        <v>-9.597</v>
+        <v>-9.859500000000001</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.37</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.606</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="J150" t="n">
-        <v>-12.726</v>
+        <v>-12.7764</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.2</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7631</v>
+        <v>-0.7528</v>
       </c>
       <c r="J151" t="n">
-        <v>-16.0251</v>
+        <v>-15.8088</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.44</v>
       </c>
       <c r="I152" t="n">
-        <v>0.9216</v>
+        <v>0.8612</v>
       </c>
       <c r="J152" t="n">
-        <v>23.04</v>
+        <v>21.53</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.9</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1225</v>
+        <v>-0.138</v>
       </c>
       <c r="J153" t="n">
-        <v>-3.0625</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.78</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2439</v>
+        <v>-0.2604</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.0975</v>
+        <v>-6.51</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.76</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2635</v>
+        <v>-0.2796</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.5875</v>
+        <v>-6.99</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.51</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4979</v>
+        <v>-0.5046</v>
       </c>
       <c r="J156" t="n">
-        <v>-12.4475</v>
+        <v>-12.615</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>2.02</v>
       </c>
       <c r="I157" t="n">
-        <v>1.7497</v>
+        <v>1.7487</v>
       </c>
       <c r="J157" t="n">
-        <v>43.7425</v>
+        <v>43.7175</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.28</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7321</v>
+        <v>0.7019</v>
       </c>
       <c r="J158" t="n">
-        <v>18.3025</v>
+        <v>17.5475</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.22</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5949</v>
+        <v>0.5793</v>
       </c>
       <c r="J159" t="n">
-        <v>14.8725</v>
+        <v>14.4825</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.17</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4719</v>
+        <v>0.4687</v>
       </c>
       <c r="J160" t="n">
-        <v>11.7975</v>
+        <v>11.7175</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.9644</v>
+        <v>-0.8771</v>
       </c>
       <c r="J161" t="n">
-        <v>-24.11</v>
+        <v>-21.9275</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.11</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2923</v>
+        <v>0.2906</v>
       </c>
       <c r="J162" t="n">
-        <v>7.5998</v>
+        <v>7.5556</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.98</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0283</v>
+        <v>-0.0369</v>
       </c>
       <c r="J163" t="n">
-        <v>-0.7358</v>
+        <v>-0.9594</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.96</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0561</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="J164" t="n">
-        <v>-1.4586</v>
+        <v>-1.7446</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.79</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2388</v>
+        <v>-0.2544</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.2088</v>
+        <v>-6.6144</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.74</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2878</v>
+        <v>-0.3025</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.4828</v>
+        <v>-7.865</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.42</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0533</v>
+        <v>1.0006</v>
       </c>
       <c r="J167" t="n">
-        <v>27.3858</v>
+        <v>26.0156</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.19</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5486</v>
+        <v>0.532</v>
       </c>
       <c r="J168" t="n">
-        <v>14.2636</v>
+        <v>13.832</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.04</v>
       </c>
       <c r="I169" t="n">
-        <v>0.1356</v>
+        <v>0.1492</v>
       </c>
       <c r="J169" t="n">
-        <v>3.5256</v>
+        <v>3.8792</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.04</v>
       </c>
       <c r="I170" t="n">
-        <v>0.1356</v>
+        <v>0.1492</v>
       </c>
       <c r="J170" t="n">
-        <v>3.5256</v>
+        <v>3.8792</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.98</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1277</v>
+        <v>-0.123</v>
       </c>
       <c r="J171" t="n">
-        <v>-3.3202</v>
+        <v>-3.198</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.08</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2914</v>
+        <v>0.2758</v>
       </c>
       <c r="J172" t="n">
-        <v>6.1194</v>
+        <v>5.7918</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0689</v>
+        <v>0.0501</v>
       </c>
       <c r="J173" t="n">
-        <v>1.4469</v>
+        <v>1.0521</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.67</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3351</v>
+        <v>-0.352</v>
       </c>
       <c r="J174" t="n">
-        <v>-7.0371</v>
+        <v>-7.392</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.66</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3446</v>
+        <v>-0.3611</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.2366</v>
+        <v>-7.5831</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.46</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5308</v>
+        <v>-0.5374</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.1468</v>
+        <v>-11.2854</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.47</v>
       </c>
       <c r="I177" t="n">
-        <v>1.0763</v>
+        <v>1.0377</v>
       </c>
       <c r="J177" t="n">
-        <v>22.6023</v>
+        <v>21.7917</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.45</v>
       </c>
       <c r="I178" t="n">
-        <v>1.051</v>
+        <v>1.0076</v>
       </c>
       <c r="J178" t="n">
-        <v>22.071</v>
+        <v>21.1596</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.33</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8329</v>
+        <v>0.7931</v>
       </c>
       <c r="J179" t="n">
-        <v>17.4909</v>
+        <v>16.6551</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.3</v>
       </c>
       <c r="I180" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.7353</v>
       </c>
       <c r="J180" t="n">
-        <v>16.1196</v>
+        <v>15.4413</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.14</v>
       </c>
       <c r="I181" t="n">
-        <v>0.3801</v>
+        <v>0.3884</v>
       </c>
       <c r="J181" t="n">
-        <v>7.9821</v>
+        <v>8.1564</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.44</v>
       </c>
       <c r="I182" t="n">
-        <v>1.049</v>
+        <v>1.0026</v>
       </c>
       <c r="J182" t="n">
-        <v>24.127</v>
+        <v>23.0598</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.4</v>
       </c>
       <c r="I183" t="n">
-        <v>0.9877</v>
+        <v>0.9338</v>
       </c>
       <c r="J183" t="n">
-        <v>22.7171</v>
+        <v>21.4774</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.24</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6428</v>
+        <v>0.622</v>
       </c>
       <c r="J184" t="n">
-        <v>14.7844</v>
+        <v>14.306</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.18</v>
       </c>
       <c r="I185" t="n">
-        <v>0.498</v>
+        <v>0.4921</v>
       </c>
       <c r="J185" t="n">
-        <v>11.454</v>
+        <v>11.3183</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.1</v>
       </c>
       <c r="I186" t="n">
-        <v>0.2856</v>
+        <v>0.2985</v>
       </c>
       <c r="J186" t="n">
-        <v>6.5688</v>
+        <v>6.8655</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.3</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6853</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="J187" t="n">
-        <v>15.7619</v>
+        <v>14.8971</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.79</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2315</v>
+        <v>-0.2487</v>
       </c>
       <c r="J188" t="n">
-        <v>-5.3245</v>
+        <v>-5.7201</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.79</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2315</v>
+        <v>-0.2487</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.3245</v>
+        <v>-5.7201</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.72</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2995</v>
+        <v>-0.3153</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.8885</v>
+        <v>-7.2519</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3281</v>
+        <v>-0.3431</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.5463</v>
+        <v>-7.8913</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.06</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3516</v>
+        <v>0.3102</v>
       </c>
       <c r="J192" t="n">
-        <v>8.0868</v>
+        <v>7.1346</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.71</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.2757</v>
+        <v>-0.2989</v>
       </c>
       <c r="J193" t="n">
-        <v>-6.3411</v>
+        <v>-6.8747</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.64</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3425</v>
+        <v>-0.3631</v>
       </c>
       <c r="J194" t="n">
-        <v>-7.8775</v>
+        <v>-8.3513</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.46</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.508</v>
+        <v>-0.5194</v>
       </c>
       <c r="J195" t="n">
-        <v>-11.684</v>
+        <v>-11.9462</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.27</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6887</v>
+        <v>-0.6859</v>
       </c>
       <c r="J196" t="n">
-        <v>-15.8401</v>
+        <v>-15.7757</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>2.17</v>
       </c>
       <c r="I197" t="n">
-        <v>1.8338</v>
+        <v>1.8652</v>
       </c>
       <c r="J197" t="n">
-        <v>42.1774</v>
+        <v>42.8996</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.44</v>
       </c>
       <c r="I198" t="n">
-        <v>1.0205</v>
+        <v>0.9765</v>
       </c>
       <c r="J198" t="n">
-        <v>23.4715</v>
+        <v>22.4595</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.35</v>
       </c>
       <c r="I199" t="n">
-        <v>0.8497</v>
+        <v>0.8131</v>
       </c>
       <c r="J199" t="n">
-        <v>19.5431</v>
+        <v>18.7013</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.32</v>
       </c>
       <c r="I200" t="n">
-        <v>0.7832</v>
+        <v>0.7547</v>
       </c>
       <c r="J200" t="n">
-        <v>18.0136</v>
+        <v>17.3581</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.17</v>
       </c>
       <c r="I201" t="n">
-        <v>0.4258</v>
+        <v>0.4366</v>
       </c>
       <c r="J201" t="n">
-        <v>9.7934</v>
+        <v>10.0418</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.14</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3706</v>
+        <v>0.3609</v>
       </c>
       <c r="J202" t="n">
-        <v>9.6356</v>
+        <v>9.3834</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.92</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0997</v>
+        <v>-0.1145</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.5922</v>
+        <v>-2.977</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.89</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1329</v>
+        <v>-0.1488</v>
       </c>
       <c r="J204" t="n">
-        <v>-3.4554</v>
+        <v>-3.8688</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.78</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2434</v>
+        <v>-0.26</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.3284</v>
+        <v>-6.76</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.64</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3775</v>
+        <v>-0.3902</v>
       </c>
       <c r="J206" t="n">
-        <v>-9.815</v>
+        <v>-10.1452</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.47</v>
       </c>
       <c r="I207" t="n">
-        <v>1.0988</v>
+        <v>1.0586</v>
       </c>
       <c r="J207" t="n">
-        <v>28.5688</v>
+        <v>27.5236</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.44</v>
       </c>
       <c r="I208" t="n">
-        <v>1.06</v>
+        <v>1.0132</v>
       </c>
       <c r="J208" t="n">
-        <v>27.56</v>
+        <v>26.3432</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.35</v>
       </c>
       <c r="I209" t="n">
-        <v>0.9019</v>
+        <v>0.849</v>
       </c>
       <c r="J209" t="n">
-        <v>23.4494</v>
+        <v>22.074</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.0531</v>
+        <v>-0.0367</v>
       </c>
       <c r="J210" t="n">
-        <v>-1.3806</v>
+        <v>-0.9542</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.83</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.601</v>
+        <v>-0.5584</v>
       </c>
       <c r="J211" t="n">
-        <v>-15.626</v>
+        <v>-14.5184</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.33</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.8359</v>
       </c>
       <c r="J212" t="n">
-        <v>42.9456</v>
+        <v>40.1232</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.24</v>
       </c>
       <c r="I213" t="n">
-        <v>0.6795</v>
+        <v>0.6471</v>
       </c>
       <c r="J213" t="n">
-        <v>32.616</v>
+        <v>31.0608</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.2</v>
       </c>
       <c r="I214" t="n">
-        <v>0.5807</v>
+        <v>0.5592</v>
       </c>
       <c r="J214" t="n">
-        <v>27.8736</v>
+        <v>26.8416</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.09</v>
       </c>
       <c r="I215" t="n">
-        <v>0.2944</v>
+        <v>0.2979</v>
       </c>
       <c r="J215" t="n">
-        <v>14.1312</v>
+        <v>14.2992</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.68</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.9516</v>
+        <v>-0.8719</v>
       </c>
       <c r="J216" t="n">
-        <v>-45.6768</v>
+        <v>-41.8512</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.18</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4042</v>
+        <v>0.4011</v>
       </c>
       <c r="J217" t="n">
-        <v>19.4016</v>
+        <v>19.2528</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.18</v>
       </c>
       <c r="I218" t="n">
-        <v>0.4042</v>
+        <v>0.4011</v>
       </c>
       <c r="J218" t="n">
-        <v>19.4016</v>
+        <v>19.2528</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.93</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0992</v>
+        <v>-0.1109</v>
       </c>
       <c r="J219" t="n">
-        <v>-4.7616</v>
+        <v>-5.3232</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.93</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0992</v>
+        <v>-0.1109</v>
       </c>
       <c r="J220" t="n">
-        <v>-4.7616</v>
+        <v>-5.3232</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.74</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2971</v>
+        <v>-0.3097</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.2608</v>
+        <v>-14.8656</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.44</v>
       </c>
       <c r="I222" t="n">
-        <v>1.0735</v>
+        <v>1.0264</v>
       </c>
       <c r="J222" t="n">
-        <v>28.9845</v>
+        <v>27.7128</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.27</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7351</v>
+        <v>0.6993</v>
       </c>
       <c r="J223" t="n">
-        <v>19.8477</v>
+        <v>18.8811</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.12</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3665</v>
+        <v>0.3671</v>
       </c>
       <c r="J224" t="n">
-        <v>9.8955</v>
+        <v>9.9117</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.11</v>
       </c>
       <c r="I225" t="n">
-        <v>0.3394</v>
+        <v>0.3422</v>
       </c>
       <c r="J225" t="n">
-        <v>9.1638</v>
+        <v>9.2394</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.86</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5059</v>
+        <v>-0.4756</v>
       </c>
       <c r="J226" t="n">
-        <v>-13.6593</v>
+        <v>-12.8412</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.41</v>
       </c>
       <c r="I227" t="n">
-        <v>0.8028</v>
+        <v>0.7649</v>
       </c>
       <c r="J227" t="n">
-        <v>21.6756</v>
+        <v>20.6523</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.01</v>
       </c>
       <c r="I228" t="n">
-        <v>0.0372</v>
+        <v>0.043</v>
       </c>
       <c r="J228" t="n">
-        <v>1.0044</v>
+        <v>1.161</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.93</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1005</v>
+        <v>-0.1118</v>
       </c>
       <c r="J229" t="n">
-        <v>-2.7135</v>
+        <v>-3.0186</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.91</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1235</v>
+        <v>-0.1358</v>
       </c>
       <c r="J230" t="n">
-        <v>-3.3345</v>
+        <v>-3.6666</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.76</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.279</v>
+        <v>-0.2918</v>
       </c>
       <c r="J231" t="n">
-        <v>-7.533</v>
+        <v>-7.8786</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.91</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5657</v>
+        <v>1.5658</v>
       </c>
       <c r="J232" t="n">
-        <v>37.5768</v>
+        <v>37.5792</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.87</v>
       </c>
       <c r="I233" t="n">
-        <v>1.5208</v>
+        <v>1.5185</v>
       </c>
       <c r="J233" t="n">
-        <v>36.4992</v>
+        <v>36.444</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.35</v>
       </c>
       <c r="I234" t="n">
-        <v>0.8505</v>
+        <v>0.8136</v>
       </c>
       <c r="J234" t="n">
-        <v>20.412</v>
+        <v>19.5264</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.17</v>
       </c>
       <c r="I235" t="n">
-        <v>0.4266</v>
+        <v>0.4371</v>
       </c>
       <c r="J235" t="n">
-        <v>10.2384</v>
+        <v>10.4904</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.13</v>
       </c>
       <c r="I236" t="n">
-        <v>0.3216</v>
+        <v>0.3418</v>
       </c>
       <c r="J236" t="n">
-        <v>7.7184</v>
+        <v>8.203200000000001</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>0.96</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.0127</v>
+        <v>-0.0332</v>
       </c>
       <c r="J237" t="n">
-        <v>-0.3048</v>
+        <v>-0.7968</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.72</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2807</v>
+        <v>-0.3009</v>
       </c>
       <c r="J238" t="n">
-        <v>-6.7368</v>
+        <v>-7.2216</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.7</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2983</v>
+        <v>-0.3182</v>
       </c>
       <c r="J239" t="n">
-        <v>-7.1592</v>
+        <v>-7.6368</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.59</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4002</v>
+        <v>-0.416</v>
       </c>
       <c r="J240" t="n">
-        <v>-9.604799999999999</v>
+        <v>-9.984</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.58</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4096</v>
+        <v>-0.4248</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.830399999999999</v>
+        <v>-10.1952</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2567/event_2567_evp_summary.xlsx
+++ b/database/event/2567/event_2567_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.1591</v>
+        <v>5.0866</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9507</v>
+        <v>0.9373</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7243</v>
+        <v>1.7114</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1591</v>
+        <v>5.0866</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1987</v>
+        <v>2.2142</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9604</v>
+        <v>2.8724</v>
       </c>
       <c r="H2" t="n">
-        <v>2.36</v>
+        <v>2.2142</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2744</v>
+        <v>1.2432</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9604</v>
+        <v>2.8724</v>
       </c>
       <c r="K2" t="n">
         <v>71</v>
@@ -529,7 +529,7 @@
         <v>161</v>
       </c>
       <c r="M2" t="n">
-        <v>4.2348</v>
+        <v>4.1156</v>
       </c>
       <c r="N2" t="n">
         <v>232</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.7561</v>
+        <v>4.5505</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8764</v>
+        <v>0.8385</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5409</v>
+        <v>1.4672</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7561</v>
+        <v>4.5505</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2686</v>
+        <v>4.1412</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4875</v>
+        <v>0.4093</v>
       </c>
       <c r="H3" t="n">
-        <v>9.189399999999999</v>
+        <v>9.105399999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>4.9622</v>
+        <v>5.1124</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4875</v>
+        <v>0.4093</v>
       </c>
       <c r="K3" t="n">
         <v>183</v>
@@ -575,7 +575,7 @@
         <v>105</v>
       </c>
       <c r="M3" t="n">
-        <v>5.4497</v>
+        <v>5.5217</v>
       </c>
       <c r="N3" t="n">
         <v>288</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.3285</v>
+        <v>4.2804</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7976</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3462</v>
+        <v>1.3441</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3285</v>
+        <v>4.2804</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2208</v>
+        <v>2.2452</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1077</v>
+        <v>2.0352</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4332</v>
+        <v>2.2452</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3139</v>
+        <v>1.2606</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1077</v>
+        <v>2.0352</v>
       </c>
       <c r="K4" t="n">
         <v>71</v>
@@ -621,7 +621,7 @@
         <v>161</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4216</v>
+        <v>3.2958</v>
       </c>
       <c r="N4" t="n">
         <v>232</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.9513</v>
+        <v>3.839</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7281</v>
+        <v>0.7074</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1745</v>
+        <v>1.1431</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9513</v>
+        <v>3.839</v>
       </c>
       <c r="F5" t="n">
-        <v>3.279</v>
+        <v>3.2391</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6723</v>
+        <v>0.5999</v>
       </c>
       <c r="H5" t="n">
-        <v>5.9245</v>
+        <v>5.7184</v>
       </c>
       <c r="I5" t="n">
-        <v>3.1992</v>
+        <v>3.2107</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6723</v>
+        <v>0.5999</v>
       </c>
       <c r="K5" t="n">
         <v>140</v>
@@ -667,7 +667,7 @@
         <v>81</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8715</v>
+        <v>3.8106</v>
       </c>
       <c r="N5" t="n">
         <v>221</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8555</v>
+        <v>3.7774</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7105</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1309</v>
+        <v>1.115</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8555</v>
+        <v>3.7774</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2135</v>
+        <v>2.234</v>
       </c>
       <c r="G6" t="n">
-        <v>1.642</v>
+        <v>1.5434</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4091</v>
+        <v>2.234</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3009</v>
+        <v>1.2543</v>
       </c>
       <c r="J6" t="n">
-        <v>1.642</v>
+        <v>1.5434</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
@@ -713,7 +713,7 @@
         <v>137</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9429</v>
+        <v>2.7977</v>
       </c>
       <c r="N6" t="n">
         <v>187</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5464</v>
+        <v>3.5397</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6535</v>
+        <v>0.6523</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9902</v>
+        <v>1.0067</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5464</v>
+        <v>3.5397</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2668</v>
+        <v>3.017</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2796</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>5.8842</v>
+        <v>4.8847</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1774</v>
+        <v>2.7426</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2796</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>183</v>
+        <v>71</v>
       </c>
       <c r="L7" t="n">
-        <v>105</v>
+        <v>161</v>
       </c>
       <c r="M7" t="n">
-        <v>3.457</v>
+        <v>3.2653</v>
       </c>
       <c r="N7" t="n">
-        <v>288</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5431</v>
+        <v>3.4313</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6529</v>
+        <v>0.6323</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9887</v>
+        <v>0.9573</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5431</v>
+        <v>3.4313</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9995</v>
+        <v>3.2123</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5436</v>
+        <v>0.219</v>
       </c>
       <c r="H8" t="n">
-        <v>5.0021</v>
+        <v>5.6176</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7011</v>
+        <v>3.1541</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5436</v>
+        <v>0.219</v>
       </c>
       <c r="K8" t="n">
-        <v>71</v>
+        <v>183</v>
       </c>
       <c r="L8" t="n">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2447</v>
+        <v>3.3731</v>
       </c>
       <c r="N8" t="n">
-        <v>232</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.241</v>
+        <v>3.2579</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5972</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8512</v>
+        <v>0.8783</v>
       </c>
       <c r="E9" t="n">
-        <v>3.241</v>
+        <v>3.2579</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2382</v>
+        <v>2.331</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0028</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4904</v>
+        <v>2.331</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3448</v>
+        <v>1.3088</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0028</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="K9" t="n">
         <v>50</v>
@@ -851,7 +851,7 @@
         <v>137</v>
       </c>
       <c r="M9" t="n">
-        <v>2.3476</v>
+        <v>2.2357</v>
       </c>
       <c r="N9" t="n">
         <v>187</v>
@@ -860,35 +860,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0082</v>
+        <v>2.9651</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5543</v>
+        <v>0.5464</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7452</v>
+        <v>0.745</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0082</v>
+        <v>2.9651</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9966</v>
+        <v>2.7948</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0116</v>
+        <v>0.1703</v>
       </c>
       <c r="H10" t="n">
-        <v>4.9927</v>
+        <v>4.0503</v>
       </c>
       <c r="I10" t="n">
-        <v>2.696</v>
+        <v>2.2741</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0116</v>
+        <v>0.1703</v>
       </c>
       <c r="K10" t="n">
         <v>140</v>
@@ -897,7 +897,7 @@
         <v>81</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7076</v>
+        <v>2.4444</v>
       </c>
       <c r="N10" t="n">
         <v>221</v>
@@ -906,139 +906,139 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9839</v>
+        <v>2.9549</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5498</v>
+        <v>0.5445</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7341</v>
+        <v>0.7403</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9839</v>
+        <v>2.9549</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1521</v>
+        <v>2.9457</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8318</v>
+        <v>0.0092</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2063</v>
+        <v>4.617</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1914</v>
+        <v>2.5923</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8318</v>
+        <v>0.0092</v>
       </c>
       <c r="K11" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="L11" t="n">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0232</v>
+        <v>2.6015</v>
       </c>
       <c r="N11" t="n">
-        <v>187</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9264</v>
+        <v>2.8956</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5392</v>
+        <v>0.5336</v>
       </c>
       <c r="D12" t="n">
-        <v>0.708</v>
+        <v>0.7133</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9264</v>
+        <v>2.8956</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7349</v>
+        <v>2.3867</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1915</v>
+        <v>0.5089</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1293</v>
+        <v>2.5182</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2298</v>
+        <v>1.4139</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1915</v>
+        <v>0.5089</v>
       </c>
       <c r="K12" t="n">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="L12" t="n">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="M12" t="n">
-        <v>2.4213</v>
+        <v>1.9228</v>
       </c>
       <c r="N12" t="n">
-        <v>221</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8269</v>
+        <v>2.8202</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5209</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6627</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8269</v>
+        <v>2.8202</v>
       </c>
       <c r="F13" t="n">
-        <v>2.303</v>
+        <v>2.0094</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5239</v>
+        <v>0.8108</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7041</v>
+        <v>2.0094</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4602</v>
+        <v>1.1282</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5239</v>
+        <v>0.8108</v>
       </c>
       <c r="K13" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="L13" t="n">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9841</v>
+        <v>1.939</v>
       </c>
       <c r="N13" t="n">
-        <v>232</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7901</v>
+        <v>2.7895</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5141</v>
+        <v>0.514</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6459</v>
+        <v>0.665</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7901</v>
+        <v>2.7895</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5643</v>
+        <v>2.6367</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2258</v>
+        <v>0.1528</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5665</v>
+        <v>3.4566</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9259</v>
+        <v>1.9408</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2258</v>
+        <v>0.1528</v>
       </c>
       <c r="K14" t="n">
         <v>140</v>
@@ -1081,7 +1081,7 @@
         <v>81</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1517</v>
+        <v>2.0936</v>
       </c>
       <c r="N14" t="n">
         <v>221</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6129</v>
+        <v>2.6895</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4815</v>
+        <v>0.4956</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5652</v>
+        <v>0.6194</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6129</v>
+        <v>2.6895</v>
       </c>
       <c r="F15" t="n">
-        <v>2.227</v>
+        <v>2.3059</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3859</v>
+        <v>0.3836</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4536</v>
+        <v>2.3059</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3249</v>
+        <v>1.2947</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3859</v>
+        <v>0.3836</v>
       </c>
       <c r="K15" t="n">
         <v>50</v>
@@ -1127,7 +1127,7 @@
         <v>137</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7108</v>
+        <v>1.6783</v>
       </c>
       <c r="N15" t="n">
         <v>187</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3036</v>
+        <v>2.1633</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4245</v>
+        <v>0.3986</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4244</v>
+        <v>0.3797</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3036</v>
+        <v>2.1633</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8967</v>
+        <v>1.8209</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4069</v>
+        <v>0.3424</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8967</v>
+        <v>1.8209</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0242</v>
+        <v>1.0224</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4069</v>
+        <v>0.3424</v>
       </c>
       <c r="K16" t="n">
         <v>183</v>
@@ -1173,7 +1173,7 @@
         <v>105</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4311</v>
+        <v>1.3648</v>
       </c>
       <c r="N16" t="n">
         <v>288</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1323</v>
+        <v>1.9724</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3929</v>
+        <v>0.3635</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3465</v>
+        <v>0.2927</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1323</v>
+        <v>1.9724</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1323</v>
+        <v>1.9724</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1323</v>
+        <v>1.9724</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1323</v>
+        <v>1.9724</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.1323</v>
+        <v>1.9724</v>
       </c>
       <c r="N17" t="n">
         <v>131</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7671</v>
+        <v>1.9228</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3256</v>
+        <v>0.3543</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1802</v>
+        <v>0.2701</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7671</v>
+        <v>1.9228</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3937</v>
+        <v>2.5004</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6266</v>
+        <v>-0.5776</v>
       </c>
       <c r="H18" t="n">
-        <v>3.0034</v>
+        <v>2.945</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6218</v>
+        <v>1.6535</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6266</v>
+        <v>-0.5776</v>
       </c>
       <c r="K18" t="n">
         <v>140</v>
@@ -1265,7 +1265,7 @@
         <v>81</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9951999999999999</v>
+        <v>1.0759</v>
       </c>
       <c r="N18" t="n">
         <v>221</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4186</v>
+        <v>1.4125</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2614</v>
+        <v>0.2603</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0216</v>
+        <v>0.0377</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4186</v>
+        <v>1.4125</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4186</v>
+        <v>1.4125</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4186</v>
+        <v>1.4125</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4186</v>
+        <v>1.4125</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4186</v>
+        <v>1.4125</v>
       </c>
       <c r="N19" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4183</v>
+        <v>1.2811</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2614</v>
+        <v>0.2361</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0214</v>
+        <v>-0.0222</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4183</v>
+        <v>1.2811</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4183</v>
+        <v>1.2811</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4183</v>
+        <v>1.2811</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4183</v>
+        <v>1.2811</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4183</v>
+        <v>1.2811</v>
       </c>
       <c r="N20" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1611</v>
+        <v>1.1781</v>
       </c>
       <c r="C21" t="n">
-        <v>0.214</v>
+        <v>0.2171</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0956</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1611</v>
+        <v>1.1781</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2711</v>
+        <v>0.2825</v>
       </c>
       <c r="G21" t="n">
-        <v>0.89</v>
+        <v>0.8956</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2711</v>
+        <v>0.2825</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1464</v>
+        <v>0.1586</v>
       </c>
       <c r="J21" t="n">
-        <v>0.89</v>
+        <v>0.8956</v>
       </c>
       <c r="K21" t="n">
         <v>50</v>
@@ -1403,7 +1403,7 @@
         <v>137</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0364</v>
+        <v>1.0542</v>
       </c>
       <c r="N21" t="n">
         <v>187</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0943</v>
+        <v>0.9766</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2016</v>
+        <v>0.18</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1261</v>
+        <v>-0.1609</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0943</v>
+        <v>0.9766</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0943</v>
+        <v>0.9766</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0943</v>
+        <v>0.9766</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0943</v>
+        <v>0.9766</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0943</v>
+        <v>0.9766</v>
       </c>
       <c r="N22" t="n">
         <v>102</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.772</v>
+        <v>0.7285</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1423</v>
+        <v>0.1342</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2728</v>
+        <v>-0.2739</v>
       </c>
       <c r="E23" t="n">
-        <v>0.772</v>
+        <v>0.7285</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9122</v>
+        <v>0.7285</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1402</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9122</v>
+        <v>0.7285</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4926</v>
+        <v>0.7285</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1402</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>183</v>
+        <v>92</v>
       </c>
       <c r="L23" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3524</v>
+        <v>0.7285</v>
       </c>
       <c r="N23" t="n">
-        <v>288</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7084</v>
+        <v>0.6742</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1305</v>
+        <v>0.1242</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3017</v>
+        <v>-0.2987</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7084</v>
+        <v>0.6742</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7084</v>
+        <v>0.6742</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7084</v>
+        <v>0.6742</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7084</v>
+        <v>0.6742</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7084</v>
+        <v>0.6742</v>
       </c>
       <c r="N24" t="n">
         <v>131</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6929</v>
+        <v>0.6249</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1277</v>
+        <v>0.1152</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3088</v>
+        <v>-0.3211</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6929</v>
+        <v>0.6249</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6929</v>
+        <v>0.6249</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6929</v>
+        <v>0.6249</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6929</v>
+        <v>0.6249</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6929</v>
+        <v>0.6249</v>
       </c>
       <c r="N25" t="n">
         <v>131</v>
@@ -1596,47 +1596,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6552</v>
+        <v>0.5493</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1207</v>
+        <v>0.1012</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3259</v>
+        <v>-0.3556</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6552</v>
+        <v>0.5493</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6552</v>
+        <v>0.7078</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.1585</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6552</v>
+        <v>0.7078</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6552</v>
+        <v>0.3974</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.1585</v>
       </c>
       <c r="K26" t="n">
-        <v>92</v>
+        <v>183</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6552</v>
+        <v>0.2389</v>
       </c>
       <c r="N26" t="n">
-        <v>92</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2654</v>
+        <v>0.2295</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0489</v>
+        <v>0.0423</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5034</v>
+        <v>-0.5012</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2654</v>
+        <v>0.2295</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2654</v>
+        <v>0.2295</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2654</v>
+        <v>0.2295</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2654</v>
+        <v>0.2295</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2654</v>
+        <v>0.2295</v>
       </c>
       <c r="N27" t="n">
         <v>102</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0532</v>
+        <v>0.0068</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0098</v>
+        <v>0.0013</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6484</v>
+        <v>-0.6027</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0532</v>
+        <v>0.0068</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0532</v>
+        <v>0.0068</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0532</v>
+        <v>0.0068</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0532</v>
+        <v>0.0068</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0532</v>
+        <v>0.0068</v>
       </c>
       <c r="N28" t="n">
-        <v>102</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.061</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0112</v>
+        <v>-0.0166</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.652</v>
+        <v>-0.6469</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.061</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.061</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.061</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.061</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.061</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>131</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0905</v>
+        <v>-0.1269</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0167</v>
+        <v>-0.0234</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6654</v>
+        <v>-0.6636</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0905</v>
+        <v>-0.1269</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0905</v>
+        <v>-0.1269</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0905</v>
+        <v>-0.1269</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0905</v>
+        <v>-0.1269</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0905</v>
+        <v>-0.1269</v>
       </c>
       <c r="N30" t="n">
         <v>92</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2938</v>
+        <v>-0.289</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0541</v>
+        <v>-0.0533</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7579</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2938</v>
+        <v>-0.289</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2938</v>
+        <v>-0.289</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2938</v>
+        <v>-0.289</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2938</v>
+        <v>-0.289</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2938</v>
+        <v>-0.289</v>
       </c>
       <c r="N31" t="n">
         <v>92</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>yel</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3118</v>
+        <v>-0.2966</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0575</v>
+        <v>-0.0547</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7661</v>
+        <v>-0.7409</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3118</v>
+        <v>-0.2966</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3118</v>
+        <v>-0.2966</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3118</v>
+        <v>-0.2966</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3118</v>
+        <v>-0.2966</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3118</v>
+        <v>-0.2966</v>
       </c>
       <c r="N32" t="n">
-        <v>102</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yel</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3179</v>
+        <v>-0.3076</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0586</v>
+        <v>-0.0567</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7689</v>
+        <v>-0.7459</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3179</v>
+        <v>-0.3076</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3179</v>
+        <v>-0.3076</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3179</v>
+        <v>-0.3076</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3179</v>
+        <v>-0.3076</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3179</v>
+        <v>-0.3076</v>
       </c>
       <c r="N33" t="n">
-        <v>71</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3946</v>
+        <v>-0.4055</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0727</v>
+        <v>-0.0747</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8038</v>
+        <v>-0.7905</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3946</v>
+        <v>-0.4055</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3946</v>
+        <v>-0.4055</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3946</v>
+        <v>-0.4055</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3946</v>
+        <v>-0.4055</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3946</v>
+        <v>-0.4055</v>
       </c>
       <c r="N34" t="n">
         <v>71</v>
@@ -2010,93 +2010,93 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>shz</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4699</v>
+        <v>-0.5119</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0866</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8381</v>
+        <v>-0.839</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.4699</v>
+        <v>-0.5119</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.4699</v>
+        <v>-0.5119</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.4699</v>
+        <v>-0.5119</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4699</v>
+        <v>-0.5119</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.4699</v>
+        <v>-0.5119</v>
       </c>
       <c r="N35" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>shz</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.4862</v>
+        <v>-0.5789</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0896</v>
+        <v>-0.1067</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8455</v>
+        <v>-0.8695000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.4862</v>
+        <v>-0.5789</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4862</v>
+        <v>-0.5789</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4862</v>
+        <v>-0.5789</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4862</v>
+        <v>-0.5789</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.4862</v>
+        <v>-0.5789</v>
       </c>
       <c r="N36" t="n">
-        <v>71</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.6075</v>
+        <v>-0.5899</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1119</v>
+        <v>-0.1087</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.8745000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.6075</v>
+        <v>-0.5899</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.6075</v>
+        <v>-0.5899</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.6075</v>
+        <v>-0.5899</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6075</v>
+        <v>-0.5899</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.6075</v>
+        <v>-0.5899</v>
       </c>
       <c r="N37" t="n">
         <v>71</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9818</v>
+        <v>-0.9356</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1809</v>
+        <v>-0.1724</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0711</v>
+        <v>-1.032</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9818</v>
+        <v>-0.9356</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9818</v>
+        <v>-0.9356</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9818</v>
+        <v>-0.9356</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9818</v>
+        <v>-0.9356</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9818</v>
+        <v>-0.9356</v>
       </c>
       <c r="N38" t="n">
         <v>71</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9993</v>
+        <v>-1.0046</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1841</v>
+        <v>-0.1851</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0791</v>
+        <v>-1.0634</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9993</v>
+        <v>-1.0046</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.8061</v>
+        <v>-0.8031</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.1932</v>
+        <v>-0.2015</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.8061</v>
+        <v>-0.8031</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4353</v>
+        <v>-0.4509</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.1932</v>
+        <v>-0.2015</v>
       </c>
       <c r="K39" t="n">
         <v>71</v>
@@ -2231,7 +2231,7 @@
         <v>161</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.6285000000000001</v>
+        <v>-0.6524000000000001</v>
       </c>
       <c r="N39" t="n">
         <v>232</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.0712</v>
+        <v>-1.0517</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1974</v>
+        <v>-0.1938</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1118</v>
+        <v>-1.0849</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.0712</v>
+        <v>-1.0517</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.0712</v>
+        <v>-1.0517</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.0712</v>
+        <v>-1.0517</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.0712</v>
+        <v>-1.0517</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.0712</v>
+        <v>-1.0517</v>
       </c>
       <c r="N40" t="n">
         <v>131</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.009</v>
+        <v>-4.0037</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7387</v>
+        <v>-0.7378</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.4492</v>
+        <v>-2.4297</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.009</v>
+        <v>-4.0037</v>
       </c>
       <c r="F41" t="n">
-        <v>-4.3628</v>
+        <v>-4.2699</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3538</v>
+        <v>0.2662</v>
       </c>
       <c r="H41" t="n">
-        <v>-4.3628</v>
+        <v>-4.2699</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.3559</v>
+        <v>-2.3974</v>
       </c>
       <c r="J41" t="n">
-        <v>0.3538</v>
+        <v>0.2662</v>
       </c>
       <c r="K41" t="n">
         <v>183</v>
@@ -2323,7 +2323,7 @@
         <v>105</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.0021</v>
+        <v>-2.1312</v>
       </c>
       <c r="N41" t="n">
         <v>288</v>
@@ -2429,10 +2429,10 @@
         <v>1.13</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3316</v>
+        <v>0.2796</v>
       </c>
       <c r="J2" t="n">
-        <v>9.284800000000001</v>
+        <v>7.8288</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.97</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0518</v>
+        <v>-0.0417</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.4504</v>
+        <v>-1.1676</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.88</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1615</v>
+        <v>-0.1427</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.522</v>
+        <v>-3.9956</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.84</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2035</v>
+        <v>-0.1836</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.698</v>
+        <v>-5.1408</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.72</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3204</v>
+        <v>-0.3034</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.9712</v>
+        <v>-8.495200000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.53</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2127</v>
+        <v>1.2304</v>
       </c>
       <c r="J7" t="n">
-        <v>33.9556</v>
+        <v>34.4512</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.22</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5958</v>
+        <v>0.5599</v>
       </c>
       <c r="J8" t="n">
-        <v>16.6824</v>
+        <v>15.6772</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2088</v>
+        <v>0.1795</v>
       </c>
       <c r="J9" t="n">
-        <v>5.8464</v>
+        <v>5.026</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1787</v>
+        <v>0.1516</v>
       </c>
       <c r="J10" t="n">
-        <v>5.0036</v>
+        <v>4.2448</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.87</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.448</v>
+        <v>-0.4063</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.544</v>
+        <v>-11.3764</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.11</v>
       </c>
       <c r="I12" t="n">
-        <v>0.275</v>
+        <v>0.2263</v>
       </c>
       <c r="J12" t="n">
-        <v>7.7</v>
+        <v>6.3364</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2555</v>
+        <v>0.2085</v>
       </c>
       <c r="J13" t="n">
-        <v>7.154</v>
+        <v>5.838</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1503</v>
+        <v>0.1156</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2084</v>
+        <v>3.2368</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.89</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1568</v>
+        <v>-0.137</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.3904</v>
+        <v>-3.836</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.77</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2803</v>
+        <v>-0.2614</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.8484</v>
+        <v>-7.3192</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.26</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6886</v>
+        <v>0.6551</v>
       </c>
       <c r="J17" t="n">
-        <v>19.2808</v>
+        <v>18.3428</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.17</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4902</v>
+        <v>0.451</v>
       </c>
       <c r="J18" t="n">
-        <v>13.7256</v>
+        <v>12.628</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.17</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4902</v>
+        <v>0.451</v>
       </c>
       <c r="J19" t="n">
-        <v>13.7256</v>
+        <v>12.628</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.12</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3722</v>
+        <v>0.3344</v>
       </c>
       <c r="J20" t="n">
-        <v>10.4216</v>
+        <v>9.363200000000001</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.85</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4917</v>
+        <v>-0.4502</v>
       </c>
       <c r="J21" t="n">
-        <v>-13.7676</v>
+        <v>-12.6056</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.13</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2507</v>
+        <v>0.2357</v>
       </c>
       <c r="J22" t="n">
-        <v>11.7829</v>
+        <v>11.0779</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1036</v>
+        <v>0.0878</v>
       </c>
       <c r="J23" t="n">
-        <v>4.8692</v>
+        <v>4.1266</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0043</v>
+        <v>0.0027</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2021</v>
+        <v>0.1269</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.83</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2178</v>
+        <v>-0.1974</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.2366</v>
+        <v>-9.277799999999999</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.76</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2869</v>
+        <v>-0.2682</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.4843</v>
+        <v>-12.6054</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.32</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4435</v>
+        <v>0.3816</v>
       </c>
       <c r="J27" t="n">
-        <v>20.8445</v>
+        <v>17.9352</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.31</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4339</v>
+        <v>0.3709</v>
       </c>
       <c r="J28" t="n">
-        <v>20.3933</v>
+        <v>17.4323</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.15</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2441</v>
+        <v>0.1957</v>
       </c>
       <c r="J29" t="n">
-        <v>11.4727</v>
+        <v>9.197900000000001</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.97</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0664</v>
+        <v>-0.0523</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.1208</v>
+        <v>-2.4581</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.78</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2811</v>
+        <v>-0.263</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.2117</v>
+        <v>-12.361</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.34</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7306</v>
+        <v>0.7159</v>
       </c>
       <c r="J32" t="n">
-        <v>20.4568</v>
+        <v>20.0452</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.33</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7159</v>
+        <v>0.7015</v>
       </c>
       <c r="J33" t="n">
-        <v>20.0452</v>
+        <v>19.642</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.33</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7159</v>
+        <v>0.7015</v>
       </c>
       <c r="J34" t="n">
-        <v>20.0452</v>
+        <v>19.642</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.09</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2841</v>
+        <v>0.2521</v>
       </c>
       <c r="J35" t="n">
-        <v>7.9548</v>
+        <v>7.0588</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.9</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3798</v>
+        <v>-0.3387</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.6344</v>
+        <v>-9.483599999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.16</v>
       </c>
       <c r="I37" t="n">
-        <v>0.378</v>
+        <v>0.3231</v>
       </c>
       <c r="J37" t="n">
-        <v>10.584</v>
+        <v>9.046799999999999</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.04</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1342</v>
+        <v>0.1014</v>
       </c>
       <c r="J38" t="n">
-        <v>3.7576</v>
+        <v>2.8392</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.02</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0819</v>
+        <v>0.0583</v>
       </c>
       <c r="J39" t="n">
-        <v>2.2932</v>
+        <v>1.6324</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.75</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2955</v>
+        <v>-0.2772</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.273999999999999</v>
+        <v>-7.7616</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.305</v>
+        <v>-0.2872</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.539999999999999</v>
+        <v>-8.041600000000001</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.31</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7122000000000001</v>
+        <v>0.6965</v>
       </c>
       <c r="J42" t="n">
-        <v>21.366</v>
+        <v>20.895</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.14</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4276</v>
+        <v>0.388</v>
       </c>
       <c r="J43" t="n">
-        <v>12.828</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.08</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2762</v>
+        <v>0.2394</v>
       </c>
       <c r="J44" t="n">
-        <v>8.286</v>
+        <v>7.182</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.99</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0494</v>
       </c>
       <c r="J45" t="n">
-        <v>-2.058</v>
+        <v>-1.482</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.79</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6231</v>
+        <v>-0.5861</v>
       </c>
       <c r="J46" t="n">
-        <v>-18.693</v>
+        <v>-17.583</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.21</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4364</v>
+        <v>0.3817</v>
       </c>
       <c r="J47" t="n">
-        <v>13.092</v>
+        <v>11.451</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.09</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2249</v>
+        <v>0.1825</v>
       </c>
       <c r="J48" t="n">
-        <v>6.747</v>
+        <v>5.475</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.03</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0953</v>
+        <v>0.0716</v>
       </c>
       <c r="J49" t="n">
-        <v>2.859</v>
+        <v>2.148</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.98</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0464</v>
+        <v>-0.035</v>
       </c>
       <c r="J50" t="n">
-        <v>-1.392</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.95</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.0902</v>
+        <v>-0.0737</v>
       </c>
       <c r="J51" t="n">
-        <v>-2.706</v>
+        <v>-2.211</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.05</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1182</v>
+        <v>0.102</v>
       </c>
       <c r="J52" t="n">
-        <v>3.546</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.03</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0804</v>
+        <v>0.0665</v>
       </c>
       <c r="J53" t="n">
-        <v>2.412</v>
+        <v>1.995</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.02</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0594</v>
+        <v>0.0474</v>
       </c>
       <c r="J54" t="n">
-        <v>1.782</v>
+        <v>1.422</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.98</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0417</v>
+        <v>-0.032</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.251</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.82</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2306</v>
+        <v>-0.2102</v>
       </c>
       <c r="J56" t="n">
-        <v>-6.918</v>
+        <v>-6.306</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.39</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5018</v>
+        <v>0.4549</v>
       </c>
       <c r="J57" t="n">
-        <v>15.054</v>
+        <v>13.647</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.27</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3896</v>
+        <v>0.3272</v>
       </c>
       <c r="J58" t="n">
-        <v>11.688</v>
+        <v>9.816000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.13</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2176</v>
+        <v>0.1728</v>
       </c>
       <c r="J59" t="n">
-        <v>6.528</v>
+        <v>5.184</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1081</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="J60" t="n">
-        <v>-3.243</v>
+        <v>-2.709</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.83</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2318</v>
+        <v>-0.2119</v>
       </c>
       <c r="J61" t="n">
-        <v>-6.954</v>
+        <v>-6.357</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.67</v>
       </c>
       <c r="I62" t="n">
-        <v>1.1494</v>
+        <v>1.1431</v>
       </c>
       <c r="J62" t="n">
-        <v>25.2868</v>
+        <v>25.1482</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.5</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9295</v>
+        <v>0.9173</v>
       </c>
       <c r="J63" t="n">
-        <v>20.449</v>
+        <v>20.1806</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.27</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6116</v>
+        <v>0.6063</v>
       </c>
       <c r="J64" t="n">
-        <v>13.4552</v>
+        <v>13.3386</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.24</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5655</v>
+        <v>0.5624</v>
       </c>
       <c r="J65" t="n">
-        <v>12.441</v>
+        <v>12.3728</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.11</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3107</v>
+        <v>0.2787</v>
       </c>
       <c r="J66" t="n">
-        <v>6.8354</v>
+        <v>6.1314</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.85</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.1827</v>
+        <v>-0.1665</v>
       </c>
       <c r="J67" t="n">
-        <v>-4.0194</v>
+        <v>-3.663</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.78</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2518</v>
+        <v>-0.2348</v>
       </c>
       <c r="J68" t="n">
-        <v>-5.5396</v>
+        <v>-5.1656</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.78</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2518</v>
+        <v>-0.2348</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.5396</v>
+        <v>-5.1656</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.76</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2703</v>
+        <v>-0.2533</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.9466</v>
+        <v>-5.5726</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.75</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2796</v>
+        <v>-0.2626</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.1512</v>
+        <v>-5.7772</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.3</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6859</v>
+        <v>0.6708</v>
       </c>
       <c r="J72" t="n">
-        <v>19.8911</v>
+        <v>19.4532</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.19</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.4956</v>
       </c>
       <c r="J73" t="n">
-        <v>14.8074</v>
+        <v>14.3724</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.14</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4195</v>
+        <v>0.3815</v>
       </c>
       <c r="J74" t="n">
-        <v>12.1655</v>
+        <v>11.0635</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.02</v>
       </c>
       <c r="I75" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="J75" t="n">
-        <v>2.4099</v>
+        <v>1.9053</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.91</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3371</v>
+        <v>-0.295</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.7759</v>
+        <v>-8.555</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.31</v>
       </c>
       <c r="I77" t="n">
-        <v>0.553</v>
+        <v>0.526</v>
       </c>
       <c r="J77" t="n">
-        <v>16.037</v>
+        <v>15.254</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.26</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4952</v>
+        <v>0.4559</v>
       </c>
       <c r="J78" t="n">
-        <v>14.3608</v>
+        <v>13.2211</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.11</v>
       </c>
       <c r="I79" t="n">
-        <v>0.26</v>
+        <v>0.2148</v>
       </c>
       <c r="J79" t="n">
-        <v>7.54</v>
+        <v>6.2292</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.99</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0307</v>
+        <v>-0.022</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.8903</v>
+        <v>-0.638</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.72</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3358</v>
+        <v>-0.3208</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.738200000000001</v>
+        <v>-9.3032</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.2</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4471</v>
+        <v>0.3899</v>
       </c>
       <c r="J82" t="n">
-        <v>12.5188</v>
+        <v>10.9172</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.96</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.0566</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.946</v>
+        <v>-1.5848</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.95</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.0828</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="J84" t="n">
-        <v>-2.3184</v>
+        <v>-1.918</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.9</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1426</v>
+        <v>-0.1238</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.9928</v>
+        <v>-3.4664</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.73</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.315</v>
+        <v>-0.2977</v>
       </c>
       <c r="J86" t="n">
-        <v>-8.82</v>
+        <v>-8.335599999999999</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.48</v>
       </c>
       <c r="I87" t="n">
-        <v>1.0736</v>
+        <v>1.0823</v>
       </c>
       <c r="J87" t="n">
-        <v>30.0608</v>
+        <v>30.3044</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.34</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.8082</v>
       </c>
       <c r="J88" t="n">
-        <v>23.2428</v>
+        <v>22.6296</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.27</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6895</v>
+        <v>0.6599</v>
       </c>
       <c r="J89" t="n">
-        <v>19.306</v>
+        <v>18.4772</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.06</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1973</v>
+        <v>0.1693</v>
       </c>
       <c r="J90" t="n">
-        <v>5.5244</v>
+        <v>4.7404</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.92</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.328</v>
+        <v>-0.288</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.183999999999999</v>
+        <v>-8.064</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.33</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4473</v>
+        <v>0.382</v>
       </c>
       <c r="J92" t="n">
-        <v>12.5244</v>
+        <v>10.696</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.32</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4363</v>
+        <v>0.3717</v>
       </c>
       <c r="J93" t="n">
-        <v>12.2164</v>
+        <v>10.4076</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.31</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4253</v>
+        <v>0.3614</v>
       </c>
       <c r="J94" t="n">
-        <v>11.9084</v>
+        <v>10.1192</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.16</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2513</v>
+        <v>0.2041</v>
       </c>
       <c r="J95" t="n">
-        <v>7.0364</v>
+        <v>5.7148</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.83</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2379</v>
+        <v>-0.2189</v>
       </c>
       <c r="J96" t="n">
-        <v>-6.6612</v>
+        <v>-6.1292</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.25</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4123</v>
+        <v>0.4114</v>
       </c>
       <c r="J97" t="n">
-        <v>11.5444</v>
+        <v>11.5192</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.203</v>
+        <v>0.1861</v>
       </c>
       <c r="J98" t="n">
-        <v>5.684</v>
+        <v>5.2108</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.02</v>
       </c>
       <c r="I99" t="n">
-        <v>0.061</v>
+        <v>0.0487</v>
       </c>
       <c r="J99" t="n">
-        <v>1.708</v>
+        <v>1.3636</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.74</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3073</v>
+        <v>-0.2896</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.6044</v>
+        <v>-8.1088</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.72</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3261</v>
+        <v>-0.3095</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.130800000000001</v>
+        <v>-8.666</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.23</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5334</v>
+        <v>0.4814</v>
       </c>
       <c r="J102" t="n">
-        <v>13.8684</v>
+        <v>12.5164</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0866</v>
+        <v>-0.0735</v>
       </c>
       <c r="J103" t="n">
-        <v>-2.2516</v>
+        <v>-1.911</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.79</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2477</v>
+        <v>-0.2289</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.4402</v>
+        <v>-5.9514</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.65</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3784</v>
+        <v>-0.3652</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.8384</v>
+        <v>-9.495200000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.63</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3964</v>
+        <v>-0.3847</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.3064</v>
+        <v>-10.0022</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.7</v>
       </c>
       <c r="I107" t="n">
-        <v>1.3664</v>
+        <v>1.3908</v>
       </c>
       <c r="J107" t="n">
-        <v>35.5264</v>
+        <v>36.1608</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.57</v>
       </c>
       <c r="I108" t="n">
-        <v>1.1952</v>
+        <v>1.2099</v>
       </c>
       <c r="J108" t="n">
-        <v>31.0752</v>
+        <v>31.4574</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.18</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4997</v>
+        <v>0.4661</v>
       </c>
       <c r="J109" t="n">
-        <v>12.9922</v>
+        <v>12.1186</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.05</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1664</v>
+        <v>0.1404</v>
       </c>
       <c r="J110" t="n">
-        <v>4.3264</v>
+        <v>3.6504</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.59</v>
       </c>
       <c r="I111" t="n">
-        <v>-1.0724</v>
+        <v>-1.0847</v>
       </c>
       <c r="J111" t="n">
-        <v>-27.8824</v>
+        <v>-28.2022</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.68</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.2995</v>
+        <v>-0.2872</v>
       </c>
       <c r="J112" t="n">
-        <v>-5.391</v>
+        <v>-5.1696</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.59</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.3884</v>
+        <v>-0.3836</v>
       </c>
       <c r="J113" t="n">
-        <v>-6.9912</v>
+        <v>-6.9048</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.46</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.501</v>
+        <v>-0.5009</v>
       </c>
       <c r="J114" t="n">
-        <v>-9.018000000000001</v>
+        <v>-9.0162</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.45</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5098</v>
+        <v>-0.5102</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.176399999999999</v>
+        <v>-9.1836</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.38</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-0.5787</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.2978</v>
+        <v>-10.4166</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.84</v>
       </c>
       <c r="I117" t="n">
-        <v>1.4769</v>
+        <v>1.5073</v>
       </c>
       <c r="J117" t="n">
-        <v>26.5842</v>
+        <v>27.1314</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.76</v>
       </c>
       <c r="I118" t="n">
-        <v>1.3814</v>
+        <v>1.4067</v>
       </c>
       <c r="J118" t="n">
-        <v>24.8652</v>
+        <v>25.3206</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.76</v>
       </c>
       <c r="I119" t="n">
-        <v>1.3814</v>
+        <v>1.4067</v>
       </c>
       <c r="J119" t="n">
-        <v>24.8652</v>
+        <v>25.3206</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.25</v>
       </c>
       <c r="I120" t="n">
-        <v>0.6079</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="J120" t="n">
-        <v>10.9422</v>
+        <v>10.5156</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.083</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="J121" t="n">
-        <v>-1.494</v>
+        <v>-1.512</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.28</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5624</v>
+        <v>0.503</v>
       </c>
       <c r="J122" t="n">
-        <v>15.1848</v>
+        <v>13.581</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.12</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2887</v>
+        <v>0.2391</v>
       </c>
       <c r="J123" t="n">
-        <v>7.7949</v>
+        <v>6.4557</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.95</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.0711</v>
       </c>
       <c r="J124" t="n">
-        <v>-2.349</v>
+        <v>-1.9197</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.88</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1704</v>
+        <v>-0.15</v>
       </c>
       <c r="J125" t="n">
-        <v>-4.6008</v>
+        <v>-4.05</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.83</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2233</v>
+        <v>-0.2028</v>
       </c>
       <c r="J126" t="n">
-        <v>-6.0291</v>
+        <v>-5.4756</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.49</v>
       </c>
       <c r="I127" t="n">
-        <v>1.1106</v>
+        <v>1.1232</v>
       </c>
       <c r="J127" t="n">
-        <v>29.9862</v>
+        <v>30.3264</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.4</v>
       </c>
       <c r="I128" t="n">
-        <v>0.9707</v>
+        <v>0.9624</v>
       </c>
       <c r="J128" t="n">
-        <v>26.2089</v>
+        <v>25.9848</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2818</v>
+        <v>-0.2415</v>
       </c>
       <c r="J129" t="n">
-        <v>-7.6086</v>
+        <v>-6.5205</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.9</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3648</v>
+        <v>-0.3224</v>
       </c>
       <c r="J130" t="n">
-        <v>-9.849600000000001</v>
+        <v>-8.704800000000001</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.86</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4674</v>
+        <v>-0.4255</v>
       </c>
       <c r="J131" t="n">
-        <v>-12.6198</v>
+        <v>-11.4885</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.26</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5411</v>
+        <v>0.4825</v>
       </c>
       <c r="J132" t="n">
-        <v>15.6919</v>
+        <v>13.9925</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.01</v>
       </c>
       <c r="I133" t="n">
-        <v>0.0466</v>
+        <v>0.0312</v>
       </c>
       <c r="J133" t="n">
-        <v>1.3514</v>
+        <v>0.9048</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0027</v>
+        <v>0.0013</v>
       </c>
       <c r="J134" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.0377</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.91</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1331</v>
+        <v>-0.1144</v>
       </c>
       <c r="J135" t="n">
-        <v>-3.8599</v>
+        <v>-3.3176</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.68</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3635</v>
+        <v>-0.3497</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.5415</v>
+        <v>-10.1413</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.59</v>
       </c>
       <c r="I137" t="n">
-        <v>1.2393</v>
+        <v>1.2573</v>
       </c>
       <c r="J137" t="n">
-        <v>35.9397</v>
+        <v>36.4617</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.43</v>
       </c>
       <c r="I138" t="n">
-        <v>1.0129</v>
+        <v>1.012</v>
       </c>
       <c r="J138" t="n">
-        <v>29.3741</v>
+        <v>29.348</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.11</v>
       </c>
       <c r="I139" t="n">
-        <v>0.3436</v>
+        <v>0.3083</v>
       </c>
       <c r="J139" t="n">
-        <v>9.964399999999999</v>
+        <v>8.9407</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.92</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3165</v>
+        <v>-0.2755</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.1785</v>
+        <v>-7.9895</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.7</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.8369</v>
+        <v>-0.8187</v>
       </c>
       <c r="J141" t="n">
-        <v>-24.2701</v>
+        <v>-23.7423</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.85</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9267</v>
+        <v>0.8586</v>
       </c>
       <c r="J142" t="n">
-        <v>19.4607</v>
+        <v>18.0306</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.56</v>
       </c>
       <c r="I143" t="n">
-        <v>0.6589</v>
+        <v>0.5884</v>
       </c>
       <c r="J143" t="n">
-        <v>13.8369</v>
+        <v>12.3564</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.32</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4208</v>
+        <v>0.3621</v>
       </c>
       <c r="J144" t="n">
-        <v>8.8368</v>
+        <v>7.6041</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.22</v>
       </c>
       <c r="I145" t="n">
-        <v>0.3081</v>
+        <v>0.258</v>
       </c>
       <c r="J145" t="n">
-        <v>6.4701</v>
+        <v>5.418</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.04</v>
       </c>
       <c r="I146" t="n">
-        <v>0.0579</v>
+        <v>0.0387</v>
       </c>
       <c r="J146" t="n">
-        <v>1.2159</v>
+        <v>0.8127</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.25</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5011</v>
+        <v>0.5384</v>
       </c>
       <c r="J147" t="n">
-        <v>10.5231</v>
+        <v>11.3064</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.22</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4581</v>
+        <v>0.4869</v>
       </c>
       <c r="J148" t="n">
-        <v>9.620100000000001</v>
+        <v>10.2249</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.53</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.4695</v>
+        <v>-0.4644</v>
       </c>
       <c r="J149" t="n">
-        <v>-9.859500000000001</v>
+        <v>-9.7524</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.37</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.6228</v>
       </c>
       <c r="J150" t="n">
-        <v>-12.7764</v>
+        <v>-13.0788</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.2</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7528</v>
+        <v>-0.797</v>
       </c>
       <c r="J151" t="n">
-        <v>-15.8088</v>
+        <v>-16.737</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.44</v>
       </c>
       <c r="I152" t="n">
-        <v>0.8612</v>
+        <v>0.8249</v>
       </c>
       <c r="J152" t="n">
-        <v>21.53</v>
+        <v>20.6225</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.9</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.138</v>
+        <v>-0.1212</v>
       </c>
       <c r="J153" t="n">
-        <v>-3.45</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.78</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2604</v>
+        <v>-0.2412</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.51</v>
+        <v>-6.03</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.76</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2796</v>
+        <v>-0.2609</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.99</v>
+        <v>-6.5225</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.51</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5046</v>
+        <v>-0.5052</v>
       </c>
       <c r="J156" t="n">
-        <v>-12.615</v>
+        <v>-12.63</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>2.02</v>
       </c>
       <c r="I157" t="n">
-        <v>1.7487</v>
+        <v>1.808</v>
       </c>
       <c r="J157" t="n">
-        <v>43.7175</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.28</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7019</v>
+        <v>0.6762</v>
       </c>
       <c r="J158" t="n">
-        <v>17.5475</v>
+        <v>16.905</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.22</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5793</v>
+        <v>0.5496</v>
       </c>
       <c r="J159" t="n">
-        <v>14.4825</v>
+        <v>13.74</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.17</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4687</v>
+        <v>0.4368</v>
       </c>
       <c r="J160" t="n">
-        <v>11.7175</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.8771</v>
+        <v>-0.8668</v>
       </c>
       <c r="J161" t="n">
-        <v>-21.9275</v>
+        <v>-21.67</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.11</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2906</v>
+        <v>0.2411</v>
       </c>
       <c r="J162" t="n">
-        <v>7.5556</v>
+        <v>6.2686</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.98</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0369</v>
+        <v>-0.0288</v>
       </c>
       <c r="J163" t="n">
-        <v>-0.9594</v>
+        <v>-0.7488</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.96</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.0551</v>
       </c>
       <c r="J164" t="n">
-        <v>-1.7446</v>
+        <v>-1.4326</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.79</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2544</v>
+        <v>-0.2347</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.6144</v>
+        <v>-6.1022</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.74</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3025</v>
+        <v>-0.2845</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.865</v>
+        <v>-7.397</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.42</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0006</v>
+        <v>0.9974</v>
       </c>
       <c r="J167" t="n">
-        <v>26.0156</v>
+        <v>25.9324</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.19</v>
       </c>
       <c r="I168" t="n">
-        <v>0.532</v>
+        <v>0.4942</v>
       </c>
       <c r="J168" t="n">
-        <v>13.832</v>
+        <v>12.8492</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.04</v>
       </c>
       <c r="I169" t="n">
-        <v>0.1492</v>
+        <v>0.1244</v>
       </c>
       <c r="J169" t="n">
-        <v>3.8792</v>
+        <v>3.2344</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.04</v>
       </c>
       <c r="I170" t="n">
-        <v>0.1492</v>
+        <v>0.1244</v>
       </c>
       <c r="J170" t="n">
-        <v>3.8792</v>
+        <v>3.2344</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.98</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.123</v>
+        <v>-0.0958</v>
       </c>
       <c r="J171" t="n">
-        <v>-3.198</v>
+        <v>-2.4908</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.08</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2758</v>
+        <v>0.2353</v>
       </c>
       <c r="J172" t="n">
-        <v>5.7918</v>
+        <v>4.9413</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0501</v>
+        <v>0.0451</v>
       </c>
       <c r="J173" t="n">
-        <v>1.0521</v>
+        <v>0.9471000000000001</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.67</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.352</v>
+        <v>-0.3374</v>
       </c>
       <c r="J174" t="n">
-        <v>-7.392</v>
+        <v>-7.0854</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.66</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3611</v>
+        <v>-0.347</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.5831</v>
+        <v>-7.287</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.46</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5374</v>
+        <v>-0.5413</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.2854</v>
+        <v>-11.3673</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.47</v>
       </c>
       <c r="I177" t="n">
-        <v>1.0377</v>
+        <v>1.044</v>
       </c>
       <c r="J177" t="n">
-        <v>21.7917</v>
+        <v>21.924</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.45</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0076</v>
+        <v>1.0095</v>
       </c>
       <c r="J178" t="n">
-        <v>21.1596</v>
+        <v>21.1995</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.33</v>
       </c>
       <c r="I179" t="n">
-        <v>0.7931</v>
+        <v>0.7749</v>
       </c>
       <c r="J179" t="n">
-        <v>16.6551</v>
+        <v>16.2729</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.3</v>
       </c>
       <c r="I180" t="n">
-        <v>0.7353</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="J180" t="n">
-        <v>15.4413</v>
+        <v>14.9982</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.14</v>
       </c>
       <c r="I181" t="n">
-        <v>0.3884</v>
+        <v>0.3566</v>
       </c>
       <c r="J181" t="n">
-        <v>8.1564</v>
+        <v>7.4886</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.44</v>
       </c>
       <c r="I182" t="n">
-        <v>1.0026</v>
+        <v>1.0015</v>
       </c>
       <c r="J182" t="n">
-        <v>23.0598</v>
+        <v>23.0345</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.4</v>
       </c>
       <c r="I183" t="n">
-        <v>0.9338</v>
+        <v>0.9226</v>
       </c>
       <c r="J183" t="n">
-        <v>21.4774</v>
+        <v>21.2198</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.24</v>
       </c>
       <c r="I184" t="n">
-        <v>0.622</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="J184" t="n">
-        <v>14.306</v>
+        <v>13.6436</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.18</v>
       </c>
       <c r="I185" t="n">
-        <v>0.4921</v>
+        <v>0.4604</v>
       </c>
       <c r="J185" t="n">
-        <v>11.3183</v>
+        <v>10.5892</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.1</v>
       </c>
       <c r="I186" t="n">
-        <v>0.2985</v>
+        <v>0.2668</v>
       </c>
       <c r="J186" t="n">
-        <v>6.8655</v>
+        <v>6.1364</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.3</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.5986</v>
       </c>
       <c r="J187" t="n">
-        <v>14.8971</v>
+        <v>13.7678</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.79</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2487</v>
+        <v>-0.2297</v>
       </c>
       <c r="J188" t="n">
-        <v>-5.7201</v>
+        <v>-5.2831</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.79</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2487</v>
+        <v>-0.2297</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.7201</v>
+        <v>-5.2831</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.72</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3153</v>
+        <v>-0.2981</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.2519</v>
+        <v>-6.8563</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3431</v>
+        <v>-0.3274</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.8913</v>
+        <v>-7.5302</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.06</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3102</v>
+        <v>0.2952</v>
       </c>
       <c r="J192" t="n">
-        <v>7.1346</v>
+        <v>6.7896</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.71</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.2989</v>
+        <v>-0.2872</v>
       </c>
       <c r="J193" t="n">
-        <v>-6.8747</v>
+        <v>-6.6056</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.64</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3631</v>
+        <v>-0.3531</v>
       </c>
       <c r="J194" t="n">
-        <v>-8.3513</v>
+        <v>-8.1213</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.46</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.5194</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="J195" t="n">
-        <v>-11.9462</v>
+        <v>-11.9531</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.27</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6859</v>
+        <v>-0.7137</v>
       </c>
       <c r="J196" t="n">
-        <v>-15.7757</v>
+        <v>-16.4151</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>2.17</v>
       </c>
       <c r="I197" t="n">
-        <v>1.8652</v>
+        <v>1.9304</v>
       </c>
       <c r="J197" t="n">
-        <v>42.8996</v>
+        <v>44.3992</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.44</v>
       </c>
       <c r="I198" t="n">
-        <v>0.9765</v>
+        <v>0.9809</v>
       </c>
       <c r="J198" t="n">
-        <v>22.4595</v>
+        <v>22.5607</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.35</v>
       </c>
       <c r="I199" t="n">
-        <v>0.8131</v>
+        <v>0.8023</v>
       </c>
       <c r="J199" t="n">
-        <v>18.7013</v>
+        <v>18.4529</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.32</v>
       </c>
       <c r="I200" t="n">
-        <v>0.7547</v>
+        <v>0.7398</v>
       </c>
       <c r="J200" t="n">
-        <v>17.3581</v>
+        <v>17.0154</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.17</v>
       </c>
       <c r="I201" t="n">
-        <v>0.4366</v>
+        <v>0.4053</v>
       </c>
       <c r="J201" t="n">
-        <v>10.0418</v>
+        <v>9.321899999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.14</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3609</v>
+        <v>0.3088</v>
       </c>
       <c r="J202" t="n">
-        <v>9.3834</v>
+        <v>8.0288</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.92</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1145</v>
+        <v>-0.0992</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.977</v>
+        <v>-2.5792</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.89</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1488</v>
+        <v>-0.1315</v>
       </c>
       <c r="J204" t="n">
-        <v>-3.8688</v>
+        <v>-3.419</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.78</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.26</v>
+        <v>-0.2408</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.76</v>
+        <v>-6.2608</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.64</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3902</v>
+        <v>-0.378</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.1452</v>
+        <v>-9.827999999999999</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.47</v>
       </c>
       <c r="I207" t="n">
-        <v>1.0586</v>
+        <v>1.0654</v>
       </c>
       <c r="J207" t="n">
-        <v>27.5236</v>
+        <v>27.7004</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.44</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0132</v>
+        <v>1.0128</v>
       </c>
       <c r="J208" t="n">
-        <v>26.3432</v>
+        <v>26.3328</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.35</v>
       </c>
       <c r="I209" t="n">
-        <v>0.849</v>
+        <v>0.8285</v>
       </c>
       <c r="J209" t="n">
-        <v>22.074</v>
+        <v>21.541</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.0367</v>
+        <v>-0.0312</v>
       </c>
       <c r="J210" t="n">
-        <v>-0.9542</v>
+        <v>-0.8112</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.83</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5584</v>
+        <v>-0.5216</v>
       </c>
       <c r="J211" t="n">
-        <v>-14.5184</v>
+        <v>-13.5616</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.33</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8359</v>
+        <v>0.8122</v>
       </c>
       <c r="J212" t="n">
-        <v>40.1232</v>
+        <v>38.9856</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.24</v>
       </c>
       <c r="I213" t="n">
-        <v>0.6471</v>
+        <v>0.6116</v>
       </c>
       <c r="J213" t="n">
-        <v>31.0608</v>
+        <v>29.3568</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.2</v>
       </c>
       <c r="I214" t="n">
-        <v>0.5592</v>
+        <v>0.5208</v>
       </c>
       <c r="J214" t="n">
-        <v>26.8416</v>
+        <v>24.9984</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.09</v>
       </c>
       <c r="I215" t="n">
-        <v>0.2979</v>
+        <v>0.2623</v>
       </c>
       <c r="J215" t="n">
-        <v>14.2992</v>
+        <v>12.5904</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.68</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.8719</v>
+        <v>-0.8562</v>
       </c>
       <c r="J216" t="n">
-        <v>-41.8512</v>
+        <v>-41.0976</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.18</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4011</v>
+        <v>0.3447</v>
       </c>
       <c r="J217" t="n">
-        <v>19.2528</v>
+        <v>16.5456</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.18</v>
       </c>
       <c r="I218" t="n">
-        <v>0.4011</v>
+        <v>0.3447</v>
       </c>
       <c r="J218" t="n">
-        <v>19.2528</v>
+        <v>16.5456</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.93</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1109</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.3232</v>
+        <v>-4.4784</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.93</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1109</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="J220" t="n">
-        <v>-5.3232</v>
+        <v>-4.4784</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.74</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3097</v>
+        <v>-0.2923</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.8656</v>
+        <v>-14.0304</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.44</v>
       </c>
       <c r="I222" t="n">
-        <v>1.0264</v>
+        <v>1.0279</v>
       </c>
       <c r="J222" t="n">
-        <v>27.7128</v>
+        <v>27.7533</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.27</v>
       </c>
       <c r="I223" t="n">
-        <v>0.6993</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="J223" t="n">
-        <v>18.8811</v>
+        <v>18.0306</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.12</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3671</v>
+        <v>0.3317</v>
       </c>
       <c r="J224" t="n">
-        <v>9.9117</v>
+        <v>8.9559</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.11</v>
       </c>
       <c r="I225" t="n">
-        <v>0.3422</v>
+        <v>0.3073</v>
       </c>
       <c r="J225" t="n">
-        <v>9.2394</v>
+        <v>8.2971</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.86</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4756</v>
+        <v>-0.4346</v>
       </c>
       <c r="J226" t="n">
-        <v>-12.8412</v>
+        <v>-11.7342</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.41</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7649</v>
+        <v>0.7113</v>
       </c>
       <c r="J227" t="n">
-        <v>20.6523</v>
+        <v>19.2051</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.01</v>
       </c>
       <c r="I228" t="n">
-        <v>0.043</v>
+        <v>0.0292</v>
       </c>
       <c r="J228" t="n">
-        <v>1.161</v>
+        <v>0.7884</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.93</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1118</v>
+        <v>-0.094</v>
       </c>
       <c r="J229" t="n">
-        <v>-3.0186</v>
+        <v>-2.538</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.91</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1358</v>
+        <v>-0.1166</v>
       </c>
       <c r="J230" t="n">
-        <v>-3.6666</v>
+        <v>-3.1482</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.76</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2918</v>
+        <v>-0.2735</v>
       </c>
       <c r="J231" t="n">
-        <v>-7.8786</v>
+        <v>-7.3845</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.91</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5658</v>
+        <v>1.6021</v>
       </c>
       <c r="J232" t="n">
-        <v>37.5792</v>
+        <v>38.4504</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.87</v>
       </c>
       <c r="I233" t="n">
-        <v>1.5185</v>
+        <v>1.5513</v>
       </c>
       <c r="J233" t="n">
-        <v>36.444</v>
+        <v>37.2312</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.35</v>
       </c>
       <c r="I234" t="n">
-        <v>0.8136</v>
+        <v>0.8027</v>
       </c>
       <c r="J234" t="n">
-        <v>19.5264</v>
+        <v>19.2648</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.17</v>
       </c>
       <c r="I235" t="n">
-        <v>0.4371</v>
+        <v>0.4059</v>
       </c>
       <c r="J235" t="n">
-        <v>10.4904</v>
+        <v>9.7416</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.13</v>
       </c>
       <c r="I236" t="n">
-        <v>0.3418</v>
+        <v>0.3086</v>
       </c>
       <c r="J236" t="n">
-        <v>8.203200000000001</v>
+        <v>7.4064</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>0.96</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.0332</v>
+        <v>-0.0198</v>
       </c>
       <c r="J237" t="n">
-        <v>-0.7968</v>
+        <v>-0.4752</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.72</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.3009</v>
+        <v>-0.2866</v>
       </c>
       <c r="J238" t="n">
-        <v>-7.2216</v>
+        <v>-6.8784</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.7</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3182</v>
+        <v>-0.3041</v>
       </c>
       <c r="J239" t="n">
-        <v>-7.6368</v>
+        <v>-7.2984</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.59</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.416</v>
+        <v>-0.4061</v>
       </c>
       <c r="J240" t="n">
-        <v>-9.984</v>
+        <v>-9.7464</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.58</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4248</v>
+        <v>-0.4156</v>
       </c>
       <c r="J241" t="n">
-        <v>-10.1952</v>
+        <v>-9.974399999999999</v>
       </c>
     </row>
   </sheetData>
